--- a/business-libraries/test-data/student_case/tool.xlsx
+++ b/business-libraries/test-data/student_case/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AJ7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,96 +430,102 @@
         <v>严重度*</v>
       </c>
       <c r="J1" t="str">
-        <v>对应归因*</v>
+        <v>对应归因编码*</v>
       </c>
       <c r="K1" t="str">
+        <v>对应归因名称</v>
+      </c>
+      <c r="L1" t="str">
         <v>工具标签*</v>
       </c>
-      <c r="L1" t="str">
-        <v>作用维度</v>
-      </c>
       <c r="M1" t="str">
+        <v>作用维度编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>效果说明</v>
+      </c>
+      <c r="O1" t="str">
         <v>操作步骤摘要*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>关键话术</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>预期效果*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>单次耗时</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>疗程与频次</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>重评间隔天数</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>禁止事项*</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>禁忌说明</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>前置工具编码</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
         <v>替代工具编码</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>进阶工具编码</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Z1" t="str">
         <v>证据等级*</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AA1" t="str">
         <v>证据来源</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AB1" t="str">
         <v>效果指标</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AC1" t="str">
         <v>失败标准</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AD1" t="str">
         <v>准备事项</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AE1" t="str">
         <v>所需材料</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AF1" t="str">
         <v>输出物</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AG1" t="str">
         <v>协同工具编码</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AH1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AI1" t="str">
         <v>版本*</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AJ1" t="str">
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B2" t="str">
-        <v>行为契约模板</v>
+        <v>ABC 结构化观察记录</v>
       </c>
       <c r="C2" t="str">
-        <v>行为契约</v>
+        <v>ABC观察</v>
       </c>
       <c r="D2" t="str">
         <v>student_case</v>
       </c>
       <c r="E2" t="str">
-        <v>exercise</v>
+        <v>worksheet</v>
       </c>
       <c r="F2" t="str">
         <v>all</v>
@@ -528,102 +534,111 @@
         <v>teacher</v>
       </c>
       <c r="H2" t="str">
-        <v>感到情绪即将失控、疲惫难以恢复时</v>
+        <v>行为频繁且诱因难以识别时</v>
       </c>
       <c r="I2" t="str">
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>行为与情绪双重危机</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="K2" t="str">
-        <v>student_case,red,behavior</v>
+        <v>行为调控困难</v>
       </c>
       <c r="L2" t="str">
-        <v>情绪恢复</v>
+        <v>student_case,behavior</v>
       </c>
       <c r="M2" t="str">
-        <v>1) 离开当前情境 2) 三轮缓慢呼吸 3) 命名情绪 4) 选最小行动</v>
+        <v>SC_BEHAVIOR</v>
       </c>
       <c r="N2" t="str">
-        <v>现在先停三分钟，这三分钟只属于你自己。</v>
-      </c>
-      <c r="O2" t="str">
-        <v>单次可下降 1-2 分主观压力值</v>
+        <v>把模糊印象转成可分析的行为数据</v>
+      </c>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果
+只记录看到的，不写推测和评价
+一周后统计最高频的 A 和 C
+针对最高频的 A 做一次环境调整并观察变化</v>
       </c>
       <c r="P2" t="str">
-        <v>3 分钟</v>
+        <v>我注意到你最近有些变化，我想先了解你的感受。你可以只说一点点。</v>
       </c>
       <c r="Q2" t="str">
-        <v>每日 1-2 次，连续 7 天</v>
+        <v>识别出至少一个可干预的诱因</v>
       </c>
       <c r="R2" t="str">
-        <v>7</v>
+        <v>每次 2 分钟</v>
       </c>
       <c r="S2" t="str">
-        <v>不用于替代危机处置；出现自伤念头或持续失眠时须转介心理专员</v>
+        <v>连续 7 天</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>不要在记录中使用诊断性词汇；不要向学生展示记录表</v>
       </c>
       <c r="V2" t="str">
         <v/>
       </c>
       <c r="W2" t="str">
-        <v>ST_RX_004</v>
+        <v/>
       </c>
       <c r="X2" t="str">
-        <v>B</v>
+        <v/>
       </c>
       <c r="Y2" t="str">
-        <v>Kabat-Zinn 正念减压研究；教师群体适应性改编研究（2023）</v>
+        <v/>
       </c>
       <c r="Z2" t="str">
-        <v>主观压力值下降&gt;=1分；一周后情绪耗竭维度得分下降</v>
+        <v>A</v>
       </c>
       <c r="AA2" t="str">
-        <v>连续使用3次后主观压力值未下降</v>
+        <v>应用行为分析在班级中的实践</v>
       </c>
       <c r="AB2" t="str">
-        <v>确保教师有3分钟不被打扰的环境</v>
+        <v>一周内记录 &gt;= 8 次</v>
       </c>
       <c r="AC2" t="str">
-        <v>计时器、一周能量记录卡</v>
+        <v>一周记录不足 3 次</v>
       </c>
       <c r="AD2" t="str">
-        <v>一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE2" t="str">
-        <v>ST_RX_004</v>
+        <v>记录表</v>
       </c>
       <c r="AF2" t="str">
-        <v>学生个体问题处方库 P12</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AI2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH2" t="str">
-        <v>class_system,home_school</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>ST_RX_002</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B3" t="str">
-        <v>动机激发方案</v>
+        <v>低压力谈话框架</v>
       </c>
       <c r="C3" t="str">
-        <v>动机激发</v>
+        <v>低压谈话</v>
       </c>
       <c r="D3" t="str">
         <v>student_case</v>
       </c>
       <c r="E3" t="str">
-        <v>worksheet</v>
+        <v>script</v>
       </c>
       <c r="F3" t="str">
         <v>all</v>
@@ -632,46 +647,49 @@
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>日常自我照顾和压力管理</v>
+        <v>学生情绪明显但难以表达时</v>
       </c>
       <c r="I3" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>学业动机严重低下</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="K3" t="str">
-        <v>student_case,orange,motivation</v>
+        <v>情绪调节困难</v>
       </c>
       <c r="L3" t="str">
-        <v>自我照顾</v>
+        <v>student_case,emotion</v>
       </c>
       <c r="M3" t="str">
-        <v>1) 记录每日能量变化 2) 识别能量消耗源 3) 制定能量补充计划</v>
+        <v>SC_EMOTION</v>
       </c>
       <c r="N3" t="str">
-        <v>记录本身就是一种觉察和关爱。</v>
-      </c>
-      <c r="O3" t="str">
-        <v>帮助教师建立自我照顾习惯，降低日常压力水平</v>
+        <v>在不施压的前提下建立表达通道</v>
+      </c>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">选一个不被打扰、非正式的场合
+从一个具体的观察事实开始，不问「你怎么了」
+给出选择而非追问：「你可以只说一点点，也可以先不说」
+结束时明确下一次可以找你的时间和方式</v>
       </c>
       <c r="P3" t="str">
-        <v>5 分钟</v>
+        <v>我注意到你这两天午休都一个人待着。你可以只说一点点，不需要马上解释清楚。</v>
       </c>
       <c r="Q3" t="str">
-        <v>每日一次，持续 14 天</v>
+        <v>学生愿意做出任何程度的表达</v>
       </c>
       <c r="R3" t="str">
-        <v>14</v>
+        <v>10 分钟</v>
       </c>
       <c r="S3" t="str">
-        <v>本工具不适用于危机情境；教师处于急性心理危机时请先转介心理专员</v>
+        <v>每周一次</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U3" t="str">
-        <v/>
+        <v>不要在其他学生在场时进行；不要承诺保密后又告知他人</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -680,48 +698,54 @@
         <v/>
       </c>
       <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
         <v>B</v>
       </c>
-      <c r="Y3" t="str">
-        <v>教师自我效能感训练研究（2022）</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>连续一周能量记录完整且主观压力值下降</v>
-      </c>
       <c r="AA3" t="str">
-        <v>连续3天未记录</v>
+        <v>学生个体支持手册 第3章</v>
       </c>
       <c r="AB3" t="str">
-        <v>打印一周能量记录卡</v>
+        <v>学生做出回应（包括沉默但未回避）</v>
       </c>
       <c r="AC3" t="str">
-        <v>一周能量记录卡、笔</v>
+        <v>连续两次学生完全回避</v>
       </c>
       <c r="AD3" t="str">
-        <v>完成的一周能量记录卡</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE3" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF3" t="str">
-        <v>学生个体问题处方库 P15</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AI3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>ST_RX_003</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="B4" t="str">
-        <v>同伴支持计划</v>
+        <v>同伴联结重建方案</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴支持</v>
+        <v>同伴联结</v>
       </c>
       <c r="D4" t="str">
         <v>student_case</v>
@@ -736,46 +760,49 @@
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>需要同伴支持和经验交流时</v>
+        <v>学生被孤立或同伴冲突反复发生</v>
       </c>
       <c r="I4" t="str">
-        <v>low</v>
+        <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>学业动机严重低下</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="K4" t="str">
-        <v>student_case,yellow,peer</v>
+        <v>同伴关系受损</v>
       </c>
       <c r="L4" t="str">
-        <v>同伴支持</v>
+        <v>student_case,social</v>
       </c>
       <c r="M4" t="str">
-        <v>1) 邀请2-3位同事 2) 轮流分享当前困扰 3) 团体生成至少一条行动建议</v>
+        <v>SC_SOCIAL</v>
       </c>
       <c r="N4" t="str">
-        <v>你不是一个人在战斗。</v>
-      </c>
-      <c r="O4" t="str">
-        <v>通过结构化同伴支持缓解教师的孤立感</v>
+        <v>通过结构化任务重建同伴关系</v>
+      </c>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">找一个该学生擅长的领域，设计一个需要合作的小任务
+为其匹配一到两位关系中性的同学
+任务完成后公开肯定该学生的具体贡献
+两周后观察自然互动是否增加</v>
       </c>
       <c r="P4" t="str">
-        <v>30 分钟</v>
+        <v>这件事你最在行，你带着他们两个一起弄，周五给大家看看。</v>
       </c>
       <c r="Q4" t="str">
-        <v>每周一次，持续 4 周</v>
+        <v>自然互动频次增加</v>
       </c>
       <c r="R4" t="str">
-        <v>28</v>
+        <v>一周</v>
       </c>
       <c r="S4" t="str">
-        <v>本活动不等同于心理治疗，涉及严重心理问题时应转介专业支持</v>
+        <v>每两周一轮</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="U4" t="str">
-        <v/>
+        <v>不要公开点明该学生「需要帮助」</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -784,54 +811,60 @@
         <v/>
       </c>
       <c r="X4" t="str">
-        <v>C</v>
+        <v/>
       </c>
       <c r="Y4" t="str">
-        <v>同伴支持对教师职业倦怠干预效果研究（2021）</v>
+        <v/>
       </c>
       <c r="Z4" t="str">
-        <v>参与教师反馈压力感和孤立感下降</v>
+        <v>B</v>
       </c>
       <c r="AA4" t="str">
-        <v>连续2次参与人数低于2人</v>
+        <v>同伴关系干预实务</v>
       </c>
       <c r="AB4" t="str">
-        <v>准备问题引导卡</v>
+        <v>两周内出现自发互动</v>
       </c>
       <c r="AC4" t="str">
-        <v>问题引导卡、白板、记号笔</v>
+        <v>两轮后无变化（升级至 L2）</v>
       </c>
       <c r="AD4" t="str">
-        <v>行动建议记录表</v>
+        <v>准备记录表</v>
       </c>
       <c r="AE4" t="str">
-        <v/>
+        <v>记录表</v>
       </c>
       <c r="AF4" t="str">
-        <v>学生个体问题处方库 P20</v>
+        <v>一次执行记录</v>
       </c>
       <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AI4" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
+      <c r="AJ4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>ST_RX_004</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="B5" t="str">
-        <v>个体辅导框架</v>
+        <v>三级支持决策卡</v>
       </c>
       <c r="C5" t="str">
-        <v>个体辅导</v>
+        <v>分级决策</v>
       </c>
       <c r="D5" t="str">
         <v>student_case</v>
       </c>
       <c r="E5" t="str">
-        <v>script</v>
+        <v>checklist</v>
       </c>
       <c r="F5" t="str">
         <v>all</v>
@@ -840,97 +873,332 @@
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>出现明显负面自动思维时</v>
+        <v>需要判断由教师支持、年级协同还是专业会商</v>
       </c>
       <c r="I5" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="J5" t="str">
-        <v>行为与情绪双重危机</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="K5" t="str">
-        <v>student_case,red,individual</v>
+        <v>适应障碍信号</v>
       </c>
       <c r="L5" t="str">
-        <v>认知调整</v>
+        <v>student_case,adapt</v>
       </c>
       <c r="M5" t="str">
-        <v>1) 识别负面自动思维 2) 检验思维的证据 3) 生成替代性解释 4) 行动计划</v>
+        <v>SC_ADAPT</v>
       </c>
       <c r="N5" t="str">
-        <v>想法不一定是事实，让我们一起来看看证据。</v>
-      </c>
-      <c r="O5" t="str">
-        <v>帮助教师识别和调整负面自动思维，降低认知层面的压力</v>
+        <v>让支持层级的判断有据可依</v>
+      </c>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">整理问题的起止时间线和关键事件
+列出已尝试的支持措施和各自效果
+对照三级标准判断当前层级
+按层级准备对应材料并启动流程</v>
       </c>
       <c r="P5" t="str">
+        <v>目前我们先基于观察事实协同支持，不做标签判断，重点是看哪些支持对学生有效。</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>形成一份可交接的支持材料</v>
+      </c>
+      <c r="R5" t="str">
+        <v>30 分钟</v>
+      </c>
+      <c r="S5" t="str">
+        <v>每次层级变化时</v>
+      </c>
+      <c r="T5" t="str">
+        <v>30</v>
+      </c>
+      <c r="U5" t="str">
+        <v>不得在材料中写入诊断性结论</v>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>学生个体支持手册 第6章</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>材料包含时间线、措施和效果三部分</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>无法回忆已尝试过哪些措施</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>SC_RX_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>学业交叉评估转介单</v>
+      </c>
+      <c r="C6" t="str">
+        <v>学业转介</v>
+      </c>
+      <c r="D6" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E6" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F6" t="str">
+        <v>all</v>
+      </c>
+      <c r="G6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H6" t="str">
+        <v>学业下降是最突出的表现时</v>
+      </c>
+      <c r="I6" t="str">
+        <v>low</v>
+      </c>
+      <c r="J6" t="str">
+        <v>SC_AT_ACADEMIC</v>
+      </c>
+      <c r="K6" t="str">
+        <v>学业功能下降</v>
+      </c>
+      <c r="L6" t="str">
+        <v>student_case,academic</v>
+      </c>
+      <c r="M6" t="str">
+        <v>SC_ACADEMIC</v>
+      </c>
+      <c r="N6" t="str">
+        <v>把学业问题转到学习问题模块做精准诊断</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">确认学业下降已持续四周以上
+记录哪些科目、哪些环节受影响最明显
+在学习问题模块完成三层诊断
+按三层诊断结果匹配教学支架</v>
+      </c>
+      <c r="P6" t="str">
+        <v>我们关注的不只是分数，而是他在学习过程中遇到了什么困难。</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>定位到行为、认知或关系层面的具体卡点</v>
+      </c>
+      <c r="R6" t="str">
         <v>15 分钟</v>
       </c>
-      <c r="Q5" t="str">
-        <v>每周 2-3 次，持续 4 周</v>
-      </c>
-      <c r="R5" t="str">
-        <v>14</v>
-      </c>
-      <c r="S5" t="str">
-        <v>有严重抑郁症状的教师应先在心理专员指导下使用</v>
-      </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
-        <v/>
-      </c>
-      <c r="W5" t="str">
-        <v/>
-      </c>
-      <c r="X5" t="str">
+      <c r="S6" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T6" t="str">
+        <v>30</v>
+      </c>
+      <c r="U6" t="str">
+        <v>不要在未做三层诊断前直接安排补课</v>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
         <v>B</v>
       </c>
-      <c r="Y5" t="str">
-        <v>Beck 认知疗法教师适应性改编研究（2022）</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>2周后负面自动思维频率下降 &gt;=30%</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>使用2周后负面思维频率未下降且教师反馈无改善</v>
-      </c>
-      <c r="AB5" t="str">
-        <v>打印认知重构工作表</v>
-      </c>
-      <c r="AC5" t="str">
-        <v>认知重构工作表、笔</v>
-      </c>
-      <c r="AD5" t="str">
-        <v>完成的认知重构工作表</v>
-      </c>
-      <c r="AE5" t="str">
-        <v/>
-      </c>
-      <c r="AF5" t="str">
-        <v>学生个体问题处方库 P18</v>
-      </c>
-      <c r="AG5" t="str">
+      <c r="AA6" t="str">
+        <v>跨模块协同指引</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>完成学习问题模块的三层诊断</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>诊断结果无明确主导层面</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AI6" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="AH5" t="str">
+      <c r="AJ6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>SC_RX_006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>危机转介操作卡</v>
+      </c>
+      <c r="C7" t="str">
+        <v>危机转介</v>
+      </c>
+      <c r="D7" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E7" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="F7" t="str">
+        <v>all</v>
+      </c>
+      <c r="G7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H7" t="str">
+        <v>出现拒学、躯体化或自伤相关信号</v>
+      </c>
+      <c r="I7" t="str">
+        <v>crisis</v>
+      </c>
+      <c r="J7" t="str">
+        <v>SC_AT_ADAPT</v>
+      </c>
+      <c r="K7" t="str">
+        <v>适应障碍信号</v>
+      </c>
+      <c r="L7" t="str">
+        <v>student_case,adapt,crisis</v>
+      </c>
+      <c r="M7" t="str">
+        <v>SC_ADAPT</v>
+      </c>
+      <c r="N7" t="str">
+        <v>确保危机情形被专业力量及时接住</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">确保学生当下处于安全环境并有人陪伴
+立即联系校内心理专员，说明观察到的具体事实
+同步通知年级组长和家长
+完整记录时间线，不做任何诊断性表述</v>
+      </c>
+      <c r="P7" t="str">
+        <v>我现在需要请专业老师一起来看看，我会一直陪着你。</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>在 24 小时内建立专业支持连接</v>
+      </c>
+      <c r="R7" t="str">
+        <v>立即</v>
+      </c>
+      <c r="S7" t="str">
+        <v>按需</v>
+      </c>
+      <c r="T7" t="str">
+        <v>30</v>
+      </c>
+      <c r="U7" t="str">
+        <v>严禁班主任自行判断风险等级；严禁延迟上报；严禁在学生面前讨论转介</v>
+      </c>
+      <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>校园心理危机干预规范</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>2 小时内完成专员联系</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>超过 24 小时未建立联系</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>准备记录表</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>记录表</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>一次执行记录</v>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v>学生个体问题手册v1</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AJ7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -966,95 +1234,95 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>离开当前情境</v>
+        <v>连续一周，每次行为发生时</v>
       </c>
       <c r="D2" t="str">
-        <v>暂时离开当前工作环境（办公室、教室），找到一个安静不被打扰的空间</v>
+        <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果</v>
       </c>
       <c r="E2" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>不需要走很远，去走廊尽头或空会议室即可</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>我注意到你最近有些变化，我想先了解你的感受。你可以只说一点点。</v>
       </c>
       <c r="I2" t="str">
-        <v>教师已经离开原环境，至少获得3分钟不被干扰的时间</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J2" t="str">
-        <v>如果实在无法离开怎么办？（答：至少转身背对工作区域，闭眼30秒）</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>三轮缓慢呼吸</v>
+        <v>只记录看到的，不写推测和</v>
       </c>
       <c r="D3" t="str">
-        <v>进行三轮缓慢深呼吸：吸气4秒→屏息2秒→呼气6秒。每轮之间自然呼吸10秒</v>
+        <v>只记录看到的，不写推测和评价</v>
       </c>
       <c r="E3" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>计时器（可选）</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>不要刻意用力呼吸，重点是让呼气比吸气更长</v>
+        <v/>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成了三轮呼吸</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J3" t="str">
-        <v>如果注意力无法集中怎么办？（答：把注意力放在呼气的感觉上，每次走神都重新回来即可）</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>命名此刻的情绪</v>
+        <v xml:space="preserve">一周后统计最高频的 A </v>
       </c>
       <c r="D4" t="str">
-        <v>问自己「我现在感受到的是什么？」——是愤怒、委屈、无力、焦虑、还是别的？给情绪一个名字</v>
+        <v>一周后统计最高频的 A 和 C</v>
       </c>
       <c r="E4" t="str">
-        <v>30秒</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>不需要分析原因，只需要命名。如果同时有多种情绪，选最强烈的那一个</v>
+        <v/>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>教师能够说出至少一种情绪的名称</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1062,31 +1330,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>选一个最小行动</v>
+        <v>针对最高频的 A 做一次</v>
       </c>
       <c r="D5" t="str">
-        <v>问自己「接下来5分钟，我能做的最小、最简单的一件事是什么？」选一件，然后做</v>
+        <v>针对最高频的 A 做一次环境调整并观察变化</v>
       </c>
       <c r="E5" t="str">
-        <v>60秒</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>最小行动的标准：不需要别人配合，不需要准备，立即能做</v>
+        <v/>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>教师选出了至少一个可行的最小行动</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1094,31 +1362,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ST_RX_002</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>记录今日能量</v>
+        <v>选一个不被打扰、非正式的</v>
       </c>
       <c r="D6" t="str">
-        <v>在能量记录卡上记录你今天几个关键时间点的能量状态（1-10分）</v>
+        <v>选一个不被打扰、非正式的场合</v>
       </c>
       <c r="E6" t="str">
-        <v>3分钟</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>能量记录卡</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>保持诚实，不需要美化</v>
+        <v>这一步决定后面能不能走下去</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>我注意到你这两天午休都一个人待着。你可以只说一点点，不需要马上解释清楚。</v>
       </c>
       <c r="I6" t="str">
-        <v>完成了至少3个时间点的记录</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1126,46 +1394,622 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ST_RX_002</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>识别能量消耗</v>
+        <v>从一个具体的观察事实开始</v>
       </c>
       <c r="D7" t="str">
-        <v>回顾今天的能量低谷，思考是什么消耗了你的能量</v>
+        <v>从一个具体的观察事实开始，不问「你怎么了」</v>
       </c>
       <c r="E7" t="str">
-        <v>2分钟</v>
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>不需要找出所有原因，选影响最大的1-2个即可</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>识别出至少1个能量消耗源</v>
+        <v>完成本步骤描述的动作</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SC_RX_002</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>给出选择而非追问：「你可</v>
+      </c>
+      <c r="D8" t="str">
+        <v>给出选择而非追问：「你可以只说一点点，也可以先不说」</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SC_RX_002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>结束时明确下一次可以找你</v>
+      </c>
+      <c r="D9" t="str">
+        <v>结束时明确下一次可以找你的时间和方式</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SC_RX_003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>找一个该学生擅长的领域，</v>
+      </c>
+      <c r="D10" t="str">
+        <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H10" t="str">
+        <v>这件事你最在行，你带着他们两个一起弄，周五给大家看看。</v>
+      </c>
+      <c r="I10" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SC_RX_003</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>为其匹配一到两位关系中性</v>
+      </c>
+      <c r="D11" t="str">
+        <v>为其匹配一到两位关系中性的同学</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SC_RX_003</v>
+      </c>
+      <c r="B12" t="str">
+        <v>3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>任务完成后公开肯定该学生</v>
+      </c>
+      <c r="D12" t="str">
+        <v>任务完成后公开肯定该学生的具体贡献</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SC_RX_003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>4</v>
+      </c>
+      <c r="C13" t="str">
+        <v>两周后观察自然互动是否增</v>
+      </c>
+      <c r="D13" t="str">
+        <v>两周后观察自然互动是否增加</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SC_RX_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>整理问题的起止时间线和关</v>
+      </c>
+      <c r="D14" t="str">
+        <v>整理问题的起止时间线和关键事件</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H14" t="str">
+        <v>目前我们先基于观察事实协同支持，不做标签判断，重点是看哪些支持对学生有效。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SC_RX_004</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2</v>
+      </c>
+      <c r="C15" t="str">
+        <v>列出已尝试的支持措施和各</v>
+      </c>
+      <c r="D15" t="str">
+        <v>列出已尝试的支持措施和各自效果</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SC_RX_004</v>
+      </c>
+      <c r="B16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>对照三级标准判断当前层级</v>
+      </c>
+      <c r="D16" t="str">
+        <v>对照三级标准判断当前层级</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SC_RX_004</v>
+      </c>
+      <c r="B17" t="str">
+        <v>4</v>
+      </c>
+      <c r="C17" t="str">
+        <v>按层级准备对应材料并启动</v>
+      </c>
+      <c r="D17" t="str">
+        <v>按层级准备对应材料并启动流程</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SC_RX_005</v>
+      </c>
+      <c r="B18" t="str">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>确认学业下降已持续四周以</v>
+      </c>
+      <c r="D18" t="str">
+        <v>确认学业下降已持续四周以上</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H18" t="str">
+        <v>我们关注的不只是分数，而是他在学习过程中遇到了什么困难。</v>
+      </c>
+      <c r="I18" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SC_RX_005</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>记录哪些科目、哪些环节受</v>
+      </c>
+      <c r="D19" t="str">
+        <v>记录哪些科目、哪些环节受影响最明显</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SC_RX_005</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>在学习问题模块完成三层诊</v>
+      </c>
+      <c r="D20" t="str">
+        <v>在学习问题模块完成三层诊断</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SC_RX_005</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>按三层诊断结果匹配教学支</v>
+      </c>
+      <c r="D21" t="str">
+        <v>按三层诊断结果匹配教学支架</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SC_RX_006</v>
+      </c>
+      <c r="B22" t="str">
+        <v>1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>确保学生当下处于安全环境</v>
+      </c>
+      <c r="D22" t="str">
+        <v>确保学生当下处于安全环境并有人陪伴</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>这一步决定后面能不能走下去</v>
+      </c>
+      <c r="H22" t="str">
+        <v>我现在需要请专业老师一起来看看，我会一直陪着你。</v>
+      </c>
+      <c r="I22" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SC_RX_006</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>立即联系校内心理专员，说</v>
+      </c>
+      <c r="D23" t="str">
+        <v>立即联系校内心理专员，说明观察到的具体事实</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SC_RX_006</v>
+      </c>
+      <c r="B24" t="str">
+        <v>3</v>
+      </c>
+      <c r="C24" t="str">
+        <v>同步通知年级组长和家长</v>
+      </c>
+      <c r="D24" t="str">
+        <v>同步通知年级组长和家长</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SC_RX_006</v>
+      </c>
+      <c r="B25" t="str">
+        <v>4</v>
+      </c>
+      <c r="C25" t="str">
+        <v>完整记录时间线，不做任何</v>
+      </c>
+      <c r="D25" t="str">
+        <v>完整记录时间线，不做任何诊断性表述</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>完成本步骤描述的动作</v>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1192,76 +2036,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ST_RX_001</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B2" t="str">
-        <v>教师自评抑郁量表得分&gt;=15</v>
+        <v>学生已在专业干预中</v>
       </c>
       <c r="C2" t="str">
-        <v>block</v>
+        <v>warn</v>
       </c>
       <c r="D2" t="str">
-        <v>抑郁风险较高时应先进行专业心理评估，不可单独依赖呼吸练习</v>
+        <v>避免重复动员造成学生压力</v>
       </c>
       <c r="E2" t="str">
-        <v>通知心理专员进行评估</v>
+        <v>与心理专员确认现有干预方案后再行动</v>
       </c>
       <c r="F2" t="str">
-        <v>存在抑郁风险的教师</v>
+        <v>班主任</v>
       </c>
       <c r="G2" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ST_RX_004</v>
-      </c>
-      <c r="B3" t="str">
-        <v>教师处于急性危机状态</v>
-      </c>
-      <c r="C3" t="str">
-        <v>block</v>
-      </c>
-      <c r="D3" t="str">
-        <v>急性危机时认知重构类工具可能加重混乱感</v>
-      </c>
-      <c r="E3" t="str">
-        <v>先使用安全稳定化工具，等状态稳定后再使用</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>PRD 8.2.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ST_RX_003</v>
-      </c>
-      <c r="B4" t="str">
-        <v>参与教师超过8人</v>
-      </c>
-      <c r="C4" t="str">
-        <v>warn</v>
-      </c>
-      <c r="D4" t="str">
-        <v>超过8人时小组讨论深度下降，建议拆分小组</v>
-      </c>
-      <c r="E4" t="str">
-        <v>每组控制在4-6人，增加一名引导员</v>
-      </c>
-      <c r="F4" t="str">
-        <v>年级组长</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>学生个体问题手册v1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/student_case/tool.xlsx
+++ b/business-libraries/test-data/student_case/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>SC_RX_001</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>ABC 结构化观察记录</v>
       </c>
       <c r="C2" t="str">
-        <v>ABC观察</v>
+        <v>ABC 结构化观</v>
       </c>
       <c r="D2" t="str">
         <v>student_case</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>SC_AT_BEHAVIOR</v>
+        <v>SC_AT_02</v>
       </c>
       <c r="K2" t="str">
         <v>行为调控困难</v>
@@ -549,16 +549,13 @@
         <v>student_case,behavior</v>
       </c>
       <c r="M2" t="str">
-        <v>SC_BEHAVIOR</v>
+        <v>SC_S1D2</v>
       </c>
       <c r="N2" t="str">
         <v>把模糊印象转成可分析的行为数据</v>
       </c>
-      <c r="O2" t="str" xml:space="preserve">
-        <v xml:space="preserve">连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果
-只记录看到的，不写推测和评价
-一周后统计最高频的 A 和 C
-针对最高频的 A 做一次环境调整并观察变化</v>
+      <c r="O2" t="str">
+        <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果；只记录看到的，不写推测和评价；一周后统计最高频的 A 和 C；针对最高频的 A 做一次环境调整并观察变化</v>
       </c>
       <c r="P2" t="str">
         <v>我注意到你最近有些变化，我想先了解你的感受。你可以只说一点点。</v>
@@ -618,21 +615,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
-        <v>SC_RX_002</v>
+        <v>SC_RX_02</v>
       </c>
       <c r="B3" t="str">
         <v>低压力谈话框架</v>
       </c>
       <c r="C3" t="str">
-        <v>低压谈话</v>
+        <v>低压力谈话框架</v>
       </c>
       <c r="D3" t="str">
         <v>student_case</v>
@@ -653,7 +650,7 @@
         <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>SC_AT_EMOTION</v>
+        <v>SC_AT_01</v>
       </c>
       <c r="K3" t="str">
         <v>情绪调节困难</v>
@@ -662,16 +659,13 @@
         <v>student_case,emotion</v>
       </c>
       <c r="M3" t="str">
-        <v>SC_EMOTION</v>
+        <v>SC_S1D3</v>
       </c>
       <c r="N3" t="str">
         <v>在不施压的前提下建立表达通道</v>
       </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">选一个不被打扰、非正式的场合
-从一个具体的观察事实开始，不问「你怎么了」
-给出选择而非追问：「你可以只说一点点，也可以先不说」
-结束时明确下一次可以找你的时间和方式</v>
+      <c r="O3" t="str">
+        <v>选一个不被打扰、非正式的场合；从一个具体的观察事实开始，不问「你怎么了」；给出选择而非追问：「你可以只说一点点，也可以先不说」；结束时明确下一次可以找你的时间和方式</v>
       </c>
       <c r="P3" t="str">
         <v>我注意到你这两天午休都一个人待着。你可以只说一点点，不需要马上解释清楚。</v>
@@ -731,21 +725,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>SC_RX_003</v>
+        <v>SC_RX_03</v>
       </c>
       <c r="B4" t="str">
         <v>同伴联结重建方案</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴联结</v>
+        <v>同伴联结重建方案</v>
       </c>
       <c r="D4" t="str">
         <v>student_case</v>
@@ -766,7 +760,7 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>SC_AT_SOCIAL</v>
+        <v>SC_AT_03</v>
       </c>
       <c r="K4" t="str">
         <v>同伴关系受损</v>
@@ -775,16 +769,13 @@
         <v>student_case,social</v>
       </c>
       <c r="M4" t="str">
-        <v>SC_SOCIAL</v>
+        <v>SC_S1D4</v>
       </c>
       <c r="N4" t="str">
         <v>通过结构化任务重建同伴关系</v>
       </c>
-      <c r="O4" t="str" xml:space="preserve">
-        <v xml:space="preserve">找一个该学生擅长的领域，设计一个需要合作的小任务
-为其匹配一到两位关系中性的同学
-任务完成后公开肯定该学生的具体贡献
-两周后观察自然互动是否增加</v>
+      <c r="O4" t="str">
+        <v>找一个该学生擅长的领域，设计一个需要合作的小任务；为其匹配一到两位关系中性的同学；任务完成后公开肯定该学生的具体贡献；两周后观察自然互动是否增加</v>
       </c>
       <c r="P4" t="str">
         <v>这件事你最在行，你带着他们两个一起弄，周五给大家看看。</v>
@@ -844,21 +835,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>SC_RX_004</v>
+        <v>SC_RX_04</v>
       </c>
       <c r="B5" t="str">
         <v>三级支持决策卡</v>
       </c>
       <c r="C5" t="str">
-        <v>分级决策</v>
+        <v>三级支持决策卡</v>
       </c>
       <c r="D5" t="str">
         <v>student_case</v>
@@ -879,25 +870,22 @@
         <v>high</v>
       </c>
       <c r="J5" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="K5" t="str">
         <v>适应障碍信号</v>
       </c>
       <c r="L5" t="str">
-        <v>student_case,adapt</v>
+        <v>student_case,adapt,crisis</v>
       </c>
       <c r="M5" t="str">
-        <v>SC_ADAPT</v>
+        <v>SC_S1D5</v>
       </c>
       <c r="N5" t="str">
         <v>让支持层级的判断有据可依</v>
       </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">整理问题的起止时间线和关键事件
-列出已尝试的支持措施和各自效果
-对照三级标准判断当前层级
-按层级准备对应材料并启动流程</v>
+      <c r="O5" t="str">
+        <v>整理问题的起止时间线和关键事件；列出已尝试的支持措施和各自效果；对照三级标准判断当前层级；按层级准备对应材料并启动流程</v>
       </c>
       <c r="P5" t="str">
         <v>目前我们先基于观察事实协同支持，不做标签判断，重点是看哪些支持对学生有效。</v>
@@ -957,21 +945,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6" t="str">
-        <v>SC_RX_005</v>
+        <v>SC_RX_05</v>
       </c>
       <c r="B6" t="str">
         <v>学业交叉评估转介单</v>
       </c>
       <c r="C6" t="str">
-        <v>学业转介</v>
+        <v>学业交叉评估转介</v>
       </c>
       <c r="D6" t="str">
         <v>student_case</v>
@@ -992,7 +980,7 @@
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>SC_AT_ACADEMIC</v>
+        <v>SC_AT_04</v>
       </c>
       <c r="K6" t="str">
         <v>学业功能下降</v>
@@ -1001,16 +989,13 @@
         <v>student_case,academic</v>
       </c>
       <c r="M6" t="str">
-        <v>SC_ACADEMIC</v>
+        <v>SC_S1D1</v>
       </c>
       <c r="N6" t="str">
         <v>把学业问题转到学习问题模块做精准诊断</v>
       </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">确认学业下降已持续四周以上
-记录哪些科目、哪些环节受影响最明显
-在学习问题模块完成三层诊断
-按三层诊断结果匹配教学支架</v>
+      <c r="O6" t="str">
+        <v>确认学业下降已持续四周以上；记录哪些科目、哪些环节受影响最明显；在学习问题模块完成三层诊断；按三层诊断结果匹配教学支架</v>
       </c>
       <c r="P6" t="str">
         <v>我们关注的不只是分数，而是他在学习过程中遇到了什么困难。</v>
@@ -1070,21 +1055,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="B7" t="str">
         <v>危机转介操作卡</v>
       </c>
       <c r="C7" t="str">
-        <v>危机转介</v>
+        <v>危机转介操作卡</v>
       </c>
       <c r="D7" t="str">
         <v>student_case</v>
@@ -1105,7 +1090,7 @@
         <v>crisis</v>
       </c>
       <c r="J7" t="str">
-        <v>SC_AT_ADAPT</v>
+        <v>SC_AT_05</v>
       </c>
       <c r="K7" t="str">
         <v>适应障碍信号</v>
@@ -1114,16 +1099,13 @@
         <v>student_case,adapt,crisis</v>
       </c>
       <c r="M7" t="str">
-        <v>SC_ADAPT</v>
+        <v>SC_S1D5</v>
       </c>
       <c r="N7" t="str">
         <v>确保危机情形被专业力量及时接住</v>
       </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">确保学生当下处于安全环境并有人陪伴
-立即联系校内心理专员，说明观察到的具体事实
-同步通知年级组长和家长
-完整记录时间线，不做任何诊断性表述</v>
+      <c r="O7" t="str">
+        <v>确保学生当下处于安全环境并有人陪伴；立即联系校内心理专员，说明观察到的具体事实；同步通知年级组长和家长；完整记录时间线，不做任何诊断性表述</v>
       </c>
       <c r="P7" t="str">
         <v>我现在需要请专业老师一起来看看，我会一直陪着你。</v>
@@ -1183,7 +1165,7 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -1234,13 +1216,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_RX_001</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>连续一周，每次行为发生时</v>
+        <v>连续一周，每次行为发生时记录三栏：A 发生前情境</v>
       </c>
       <c r="D2" t="str">
         <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果</v>
@@ -1266,13 +1248,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_RX_001</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>只记录看到的，不写推测和</v>
+        <v>只记录看到的，不写推测和评价</v>
       </c>
       <c r="D3" t="str">
         <v>只记录看到的，不写推测和评价</v>
@@ -1298,13 +1280,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_RX_001</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v xml:space="preserve">一周后统计最高频的 A </v>
+        <v>一周后统计最高频的 A 和 C</v>
       </c>
       <c r="D4" t="str">
         <v>一周后统计最高频的 A 和 C</v>
@@ -1330,13 +1312,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_RX_001</v>
+        <v>SC_RX_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>针对最高频的 A 做一次</v>
+        <v>针对最高频的 A 做一次环境调整并观察变化</v>
       </c>
       <c r="D5" t="str">
         <v>针对最高频的 A 做一次环境调整并观察变化</v>
@@ -1362,13 +1344,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_RX_002</v>
+        <v>SC_RX_02</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>选一个不被打扰、非正式的</v>
+        <v>选一个不被打扰、非正式的场合</v>
       </c>
       <c r="D6" t="str">
         <v>选一个不被打扰、非正式的场合</v>
@@ -1394,13 +1376,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_RX_002</v>
+        <v>SC_RX_02</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>从一个具体的观察事实开始</v>
+        <v>从一个具体的观察事实开始，不问「你怎么了」</v>
       </c>
       <c r="D7" t="str">
         <v>从一个具体的观察事实开始，不问「你怎么了」</v>
@@ -1426,13 +1408,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_RX_002</v>
+        <v>SC_RX_02</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>给出选择而非追问：「你可</v>
+        <v>给出选择而非追问：「你可以只说一点点，也可以先不</v>
       </c>
       <c r="D8" t="str">
         <v>给出选择而非追问：「你可以只说一点点，也可以先不说」</v>
@@ -1458,13 +1440,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_RX_002</v>
+        <v>SC_RX_02</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>结束时明确下一次可以找你</v>
+        <v>结束时明确下一次可以找你的时间和方式</v>
       </c>
       <c r="D9" t="str">
         <v>结束时明确下一次可以找你的时间和方式</v>
@@ -1490,13 +1472,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SC_RX_003</v>
+        <v>SC_RX_03</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>找一个该学生擅长的领域，</v>
+        <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
       </c>
       <c r="D10" t="str">
         <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
@@ -1522,13 +1504,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SC_RX_003</v>
+        <v>SC_RX_03</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>为其匹配一到两位关系中性</v>
+        <v>为其匹配一到两位关系中性的同学</v>
       </c>
       <c r="D11" t="str">
         <v>为其匹配一到两位关系中性的同学</v>
@@ -1554,13 +1536,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SC_RX_003</v>
+        <v>SC_RX_03</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>任务完成后公开肯定该学生</v>
+        <v>任务完成后公开肯定该学生的具体贡献</v>
       </c>
       <c r="D12" t="str">
         <v>任务完成后公开肯定该学生的具体贡献</v>
@@ -1586,13 +1568,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_RX_003</v>
+        <v>SC_RX_03</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>两周后观察自然互动是否增</v>
+        <v>两周后观察自然互动是否增加</v>
       </c>
       <c r="D13" t="str">
         <v>两周后观察自然互动是否增加</v>
@@ -1618,13 +1600,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_RX_004</v>
+        <v>SC_RX_04</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>整理问题的起止时间线和关</v>
+        <v>整理问题的起止时间线和关键事件</v>
       </c>
       <c r="D14" t="str">
         <v>整理问题的起止时间线和关键事件</v>
@@ -1650,13 +1632,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_RX_004</v>
+        <v>SC_RX_04</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>列出已尝试的支持措施和各</v>
+        <v>列出已尝试的支持措施和各自效果</v>
       </c>
       <c r="D15" t="str">
         <v>列出已尝试的支持措施和各自效果</v>
@@ -1682,7 +1664,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_RX_004</v>
+        <v>SC_RX_04</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
@@ -1714,13 +1696,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SC_RX_004</v>
+        <v>SC_RX_04</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>按层级准备对应材料并启动</v>
+        <v>按层级准备对应材料并启动流程</v>
       </c>
       <c r="D17" t="str">
         <v>按层级准备对应材料并启动流程</v>
@@ -1746,13 +1728,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SC_RX_005</v>
+        <v>SC_RX_05</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>确认学业下降已持续四周以</v>
+        <v>确认学业下降已持续四周以上</v>
       </c>
       <c r="D18" t="str">
         <v>确认学业下降已持续四周以上</v>
@@ -1778,13 +1760,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SC_RX_005</v>
+        <v>SC_RX_05</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>记录哪些科目、哪些环节受</v>
+        <v>记录哪些科目、哪些环节受影响最明显</v>
       </c>
       <c r="D19" t="str">
         <v>记录哪些科目、哪些环节受影响最明显</v>
@@ -1810,13 +1792,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SC_RX_005</v>
+        <v>SC_RX_05</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>在学习问题模块完成三层诊</v>
+        <v>在学习问题模块完成三层诊断</v>
       </c>
       <c r="D20" t="str">
         <v>在学习问题模块完成三层诊断</v>
@@ -1842,13 +1824,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SC_RX_005</v>
+        <v>SC_RX_05</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>按三层诊断结果匹配教学支</v>
+        <v>按三层诊断结果匹配教学支架</v>
       </c>
       <c r="D21" t="str">
         <v>按三层诊断结果匹配教学支架</v>
@@ -1874,13 +1856,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>确保学生当下处于安全环境</v>
+        <v>确保学生当下处于安全环境并有人陪伴</v>
       </c>
       <c r="D22" t="str">
         <v>确保学生当下处于安全环境并有人陪伴</v>
@@ -1906,13 +1888,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>立即联系校内心理专员，说</v>
+        <v>立即联系校内心理专员，说明观察到的具体事实</v>
       </c>
       <c r="D23" t="str">
         <v>立即联系校内心理专员，说明观察到的具体事实</v>
@@ -1938,7 +1920,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
@@ -1970,13 +1952,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>完整记录时间线，不做任何</v>
+        <v>完整记录时间线，不做任何诊断性表述</v>
       </c>
       <c r="D25" t="str">
         <v>完整记录时间线，不做任何诊断性表述</v>
@@ -2036,7 +2018,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_RX_006</v>
+        <v>SC_RX_06</v>
       </c>
       <c r="B2" t="str">
         <v>学生已在专业干预中</v>

--- a/business-libraries/test-data/student_case/tool.xlsx
+++ b/business-libraries/test-data/student_case/tool.xlsx
@@ -511,15 +511,15 @@
         <v>跨模块标签</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>SC_RX_01</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>ABC 结构化观察记录</v>
       </c>
       <c r="C2" t="str">
-        <v>ABC 结构化观</v>
+        <v>ABC观察</v>
       </c>
       <c r="D2" t="str">
         <v>student_case</v>
@@ -540,7 +540,7 @@
         <v>medium</v>
       </c>
       <c r="J2" t="str">
-        <v>SC_AT_02</v>
+        <v>SC_AT_BEHAVIOR</v>
       </c>
       <c r="K2" t="str">
         <v>行为调控困难</v>
@@ -549,13 +549,16 @@
         <v>student_case,behavior</v>
       </c>
       <c r="M2" t="str">
-        <v>SC_S1D2</v>
+        <v>SC_BEHAVIOR</v>
       </c>
       <c r="N2" t="str">
         <v>把模糊印象转成可分析的行为数据</v>
       </c>
-      <c r="O2" t="str">
-        <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果；只记录看到的，不写推测和评价；一周后统计最高频的 A 和 C；针对最高频的 A 做一次环境调整并观察变化</v>
+      <c r="O2" t="str" xml:space="preserve">
+        <v xml:space="preserve">连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果
+只记录看到的，不写推测和评价
+一周后统计最高频的 A 和 C
+针对最高频的 A 做一次环境调整并观察变化</v>
       </c>
       <c r="P2" t="str">
         <v>我注意到你最近有些变化，我想先了解你的感受。你可以只说一点点。</v>
@@ -615,21 +618,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B3" t="str">
         <v>低压力谈话框架</v>
       </c>
       <c r="C3" t="str">
-        <v>低压力谈话框架</v>
+        <v>低压谈话</v>
       </c>
       <c r="D3" t="str">
         <v>student_case</v>
@@ -650,7 +653,7 @@
         <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>SC_AT_01</v>
+        <v>SC_AT_EMOTION</v>
       </c>
       <c r="K3" t="str">
         <v>情绪调节困难</v>
@@ -659,13 +662,16 @@
         <v>student_case,emotion</v>
       </c>
       <c r="M3" t="str">
-        <v>SC_S1D3</v>
+        <v>SC_EMOTION</v>
       </c>
       <c r="N3" t="str">
         <v>在不施压的前提下建立表达通道</v>
       </c>
-      <c r="O3" t="str">
-        <v>选一个不被打扰、非正式的场合；从一个具体的观察事实开始，不问「你怎么了」；给出选择而非追问：「你可以只说一点点，也可以先不说」；结束时明确下一次可以找你的时间和方式</v>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">选一个不被打扰、非正式的场合
+从一个具体的观察事实开始，不问「你怎么了」
+给出选择而非追问：「你可以只说一点点，也可以先不说」
+结束时明确下一次可以找你的时间和方式</v>
       </c>
       <c r="P3" t="str">
         <v>我注意到你这两天午休都一个人待着。你可以只说一点点，不需要马上解释清楚。</v>
@@ -725,21 +731,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="B4" t="str">
         <v>同伴联结重建方案</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴联结重建方案</v>
+        <v>同伴联结</v>
       </c>
       <c r="D4" t="str">
         <v>student_case</v>
@@ -760,7 +766,7 @@
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>SC_AT_03</v>
+        <v>SC_AT_SOCIAL</v>
       </c>
       <c r="K4" t="str">
         <v>同伴关系受损</v>
@@ -769,13 +775,16 @@
         <v>student_case,social</v>
       </c>
       <c r="M4" t="str">
-        <v>SC_S1D4</v>
+        <v>SC_SOCIAL</v>
       </c>
       <c r="N4" t="str">
         <v>通过结构化任务重建同伴关系</v>
       </c>
-      <c r="O4" t="str">
-        <v>找一个该学生擅长的领域，设计一个需要合作的小任务；为其匹配一到两位关系中性的同学；任务完成后公开肯定该学生的具体贡献；两周后观察自然互动是否增加</v>
+      <c r="O4" t="str" xml:space="preserve">
+        <v xml:space="preserve">找一个该学生擅长的领域，设计一个需要合作的小任务
+为其匹配一到两位关系中性的同学
+任务完成后公开肯定该学生的具体贡献
+两周后观察自然互动是否增加</v>
       </c>
       <c r="P4" t="str">
         <v>这件事你最在行，你带着他们两个一起弄，周五给大家看看。</v>
@@ -835,21 +844,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="B5" t="str">
         <v>三级支持决策卡</v>
       </c>
       <c r="C5" t="str">
-        <v>三级支持决策卡</v>
+        <v>分级决策</v>
       </c>
       <c r="D5" t="str">
         <v>student_case</v>
@@ -870,22 +879,25 @@
         <v>high</v>
       </c>
       <c r="J5" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="K5" t="str">
         <v>适应障碍信号</v>
       </c>
       <c r="L5" t="str">
-        <v>student_case,adapt,crisis</v>
+        <v>student_case,adapt</v>
       </c>
       <c r="M5" t="str">
-        <v>SC_S1D5</v>
+        <v>SC_ADAPT</v>
       </c>
       <c r="N5" t="str">
         <v>让支持层级的判断有据可依</v>
       </c>
-      <c r="O5" t="str">
-        <v>整理问题的起止时间线和关键事件；列出已尝试的支持措施和各自效果；对照三级标准判断当前层级；按层级准备对应材料并启动流程</v>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">整理问题的起止时间线和关键事件
+列出已尝试的支持措施和各自效果
+对照三级标准判断当前层级
+按层级准备对应材料并启动流程</v>
       </c>
       <c r="P5" t="str">
         <v>目前我们先基于观察事实协同支持，不做标签判断，重点是看哪些支持对学生有效。</v>
@@ -945,21 +957,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>SC_RX_05</v>
+        <v>SC_RX_005</v>
       </c>
       <c r="B6" t="str">
         <v>学业交叉评估转介单</v>
       </c>
       <c r="C6" t="str">
-        <v>学业交叉评估转介</v>
+        <v>学业转介</v>
       </c>
       <c r="D6" t="str">
         <v>student_case</v>
@@ -980,7 +992,7 @@
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>SC_AT_04</v>
+        <v>SC_AT_ACADEMIC</v>
       </c>
       <c r="K6" t="str">
         <v>学业功能下降</v>
@@ -989,13 +1001,16 @@
         <v>student_case,academic</v>
       </c>
       <c r="M6" t="str">
-        <v>SC_S1D1</v>
+        <v>SC_ACADEMIC</v>
       </c>
       <c r="N6" t="str">
         <v>把学业问题转到学习问题模块做精准诊断</v>
       </c>
-      <c r="O6" t="str">
-        <v>确认学业下降已持续四周以上；记录哪些科目、哪些环节受影响最明显；在学习问题模块完成三层诊断；按三层诊断结果匹配教学支架</v>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">确认学业下降已持续四周以上
+记录哪些科目、哪些环节受影响最明显
+在学习问题模块完成三层诊断
+按三层诊断结果匹配教学支架</v>
       </c>
       <c r="P6" t="str">
         <v>我们关注的不只是分数，而是他在学习过程中遇到了什么困难。</v>
@@ -1055,21 +1070,21 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B7" t="str">
         <v>危机转介操作卡</v>
       </c>
       <c r="C7" t="str">
-        <v>危机转介操作卡</v>
+        <v>危机转介</v>
       </c>
       <c r="D7" t="str">
         <v>student_case</v>
@@ -1090,7 +1105,7 @@
         <v>crisis</v>
       </c>
       <c r="J7" t="str">
-        <v>SC_AT_05</v>
+        <v>SC_AT_ADAPT</v>
       </c>
       <c r="K7" t="str">
         <v>适应障碍信号</v>
@@ -1099,13 +1114,16 @@
         <v>student_case,adapt,crisis</v>
       </c>
       <c r="M7" t="str">
-        <v>SC_S1D5</v>
+        <v>SC_ADAPT</v>
       </c>
       <c r="N7" t="str">
         <v>确保危机情形被专业力量及时接住</v>
       </c>
-      <c r="O7" t="str">
-        <v>确保学生当下处于安全环境并有人陪伴；立即联系校内心理专员，说明观察到的具体事实；同步通知年级组长和家长；完整记录时间线，不做任何诊断性表述</v>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">确保学生当下处于安全环境并有人陪伴
+立即联系校内心理专员，说明观察到的具体事实
+同步通知年级组长和家长
+完整记录时间线，不做任何诊断性表述</v>
       </c>
       <c r="P7" t="str">
         <v>我现在需要请专业老师一起来看看，我会一直陪着你。</v>
@@ -1165,7 +1183,7 @@
         <v>学生个体问题手册v1</v>
       </c>
       <c r="AI7" t="str">
-        <v>4.0.0</v>
+        <v>1.0.0</v>
       </c>
       <c r="AJ7" t="str">
         <v/>
@@ -1216,13 +1234,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_RX_01</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>连续一周，每次行为发生时记录三栏：A 发生前情境</v>
+        <v>连续一周，每次行为发生时</v>
       </c>
       <c r="D2" t="str">
         <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果</v>
@@ -1248,13 +1266,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SC_RX_01</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>只记录看到的，不写推测和评价</v>
+        <v>只记录看到的，不写推测和</v>
       </c>
       <c r="D3" t="str">
         <v>只记录看到的，不写推测和评价</v>
@@ -1280,13 +1298,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SC_RX_01</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一周后统计最高频的 A 和 C</v>
+        <v xml:space="preserve">一周后统计最高频的 A </v>
       </c>
       <c r="D4" t="str">
         <v>一周后统计最高频的 A 和 C</v>
@@ -1312,13 +1330,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SC_RX_01</v>
+        <v>SC_RX_001</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>针对最高频的 A 做一次环境调整并观察变化</v>
+        <v>针对最高频的 A 做一次</v>
       </c>
       <c r="D5" t="str">
         <v>针对最高频的 A 做一次环境调整并观察变化</v>
@@ -1344,13 +1362,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B6" t="str">
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>选一个不被打扰、非正式的场合</v>
+        <v>选一个不被打扰、非正式的</v>
       </c>
       <c r="D6" t="str">
         <v>选一个不被打扰、非正式的场合</v>
@@ -1376,13 +1394,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B7" t="str">
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>从一个具体的观察事实开始，不问「你怎么了」</v>
+        <v>从一个具体的观察事实开始</v>
       </c>
       <c r="D7" t="str">
         <v>从一个具体的观察事实开始，不问「你怎么了」</v>
@@ -1408,13 +1426,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B8" t="str">
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>给出选择而非追问：「你可以只说一点点，也可以先不</v>
+        <v>给出选择而非追问：「你可</v>
       </c>
       <c r="D8" t="str">
         <v>给出选择而非追问：「你可以只说一点点，也可以先不说」</v>
@@ -1440,13 +1458,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SC_RX_02</v>
+        <v>SC_RX_002</v>
       </c>
       <c r="B9" t="str">
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>结束时明确下一次可以找你的时间和方式</v>
+        <v>结束时明确下一次可以找你</v>
       </c>
       <c r="D9" t="str">
         <v>结束时明确下一次可以找你的时间和方式</v>
@@ -1472,13 +1490,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="B10" t="str">
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
+        <v>找一个该学生擅长的领域，</v>
       </c>
       <c r="D10" t="str">
         <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
@@ -1504,13 +1522,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="B11" t="str">
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>为其匹配一到两位关系中性的同学</v>
+        <v>为其匹配一到两位关系中性</v>
       </c>
       <c r="D11" t="str">
         <v>为其匹配一到两位关系中性的同学</v>
@@ -1536,13 +1554,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="B12" t="str">
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>任务完成后公开肯定该学生的具体贡献</v>
+        <v>任务完成后公开肯定该学生</v>
       </c>
       <c r="D12" t="str">
         <v>任务完成后公开肯定该学生的具体贡献</v>
@@ -1568,13 +1586,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SC_RX_03</v>
+        <v>SC_RX_003</v>
       </c>
       <c r="B13" t="str">
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>两周后观察自然互动是否增加</v>
+        <v>两周后观察自然互动是否增</v>
       </c>
       <c r="D13" t="str">
         <v>两周后观察自然互动是否增加</v>
@@ -1600,13 +1618,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="B14" t="str">
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>整理问题的起止时间线和关键事件</v>
+        <v>整理问题的起止时间线和关</v>
       </c>
       <c r="D14" t="str">
         <v>整理问题的起止时间线和关键事件</v>
@@ -1632,13 +1650,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="B15" t="str">
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>列出已尝试的支持措施和各自效果</v>
+        <v>列出已尝试的支持措施和各</v>
       </c>
       <c r="D15" t="str">
         <v>列出已尝试的支持措施和各自效果</v>
@@ -1664,7 +1682,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="B16" t="str">
         <v>3</v>
@@ -1696,13 +1714,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SC_RX_04</v>
+        <v>SC_RX_004</v>
       </c>
       <c r="B17" t="str">
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>按层级准备对应材料并启动流程</v>
+        <v>按层级准备对应材料并启动</v>
       </c>
       <c r="D17" t="str">
         <v>按层级准备对应材料并启动流程</v>
@@ -1728,13 +1746,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SC_RX_05</v>
+        <v>SC_RX_005</v>
       </c>
       <c r="B18" t="str">
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>确认学业下降已持续四周以上</v>
+        <v>确认学业下降已持续四周以</v>
       </c>
       <c r="D18" t="str">
         <v>确认学业下降已持续四周以上</v>
@@ -1760,13 +1778,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SC_RX_05</v>
+        <v>SC_RX_005</v>
       </c>
       <c r="B19" t="str">
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>记录哪些科目、哪些环节受影响最明显</v>
+        <v>记录哪些科目、哪些环节受</v>
       </c>
       <c r="D19" t="str">
         <v>记录哪些科目、哪些环节受影响最明显</v>
@@ -1792,13 +1810,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SC_RX_05</v>
+        <v>SC_RX_005</v>
       </c>
       <c r="B20" t="str">
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>在学习问题模块完成三层诊断</v>
+        <v>在学习问题模块完成三层诊</v>
       </c>
       <c r="D20" t="str">
         <v>在学习问题模块完成三层诊断</v>
@@ -1824,13 +1842,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SC_RX_05</v>
+        <v>SC_RX_005</v>
       </c>
       <c r="B21" t="str">
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>按三层诊断结果匹配教学支架</v>
+        <v>按三层诊断结果匹配教学支</v>
       </c>
       <c r="D21" t="str">
         <v>按三层诊断结果匹配教学支架</v>
@@ -1856,13 +1874,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B22" t="str">
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>确保学生当下处于安全环境并有人陪伴</v>
+        <v>确保学生当下处于安全环境</v>
       </c>
       <c r="D22" t="str">
         <v>确保学生当下处于安全环境并有人陪伴</v>
@@ -1888,13 +1906,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B23" t="str">
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>立即联系校内心理专员，说明观察到的具体事实</v>
+        <v>立即联系校内心理专员，说</v>
       </c>
       <c r="D23" t="str">
         <v>立即联系校内心理专员，说明观察到的具体事实</v>
@@ -1920,7 +1938,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B24" t="str">
         <v>3</v>
@@ -1952,13 +1970,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B25" t="str">
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>完整记录时间线，不做任何诊断性表述</v>
+        <v>完整记录时间线，不做任何</v>
       </c>
       <c r="D25" t="str">
         <v>完整记录时间线，不做任何诊断性表述</v>
@@ -2018,7 +2036,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SC_RX_06</v>
+        <v>SC_RX_006</v>
       </c>
       <c r="B2" t="str">
         <v>学生已在专业干预中</v>

--- a/business-libraries/test-data/student_case/tool.xlsx
+++ b/business-libraries/test-data/student_case/tool.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:AJ32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -516,16 +516,16 @@
         <v>SC_RX_01</v>
       </c>
       <c r="B2" t="str">
-        <v>ABC 结构化观察记录</v>
+        <v>学校安全流程响应（E2教养不当）</v>
       </c>
       <c r="C2" t="str">
-        <v>ABC 结构化观</v>
+        <v>学校安全流程响应</v>
       </c>
       <c r="D2" t="str">
         <v>student_case</v>
       </c>
       <c r="E2" t="str">
-        <v>worksheet</v>
+        <v>checklist</v>
       </c>
       <c r="F2" t="str">
         <v>all</v>
@@ -534,46 +534,46 @@
         <v>teacher</v>
       </c>
       <c r="H2" t="str">
-        <v>行为频繁且诱因难以识别时</v>
+        <v>存在体罚、言语羞辱或忽视证据；教养方式极端化；父母间教养严重不一致</v>
       </c>
       <c r="I2" t="str">
-        <v>medium</v>
+        <v>high</v>
       </c>
       <c r="J2" t="str">
-        <v>SC_AT_02</v>
+        <v>E2</v>
       </c>
       <c r="K2" t="str">
-        <v>行为调控困难</v>
+        <v>教养不当型</v>
       </c>
       <c r="L2" t="str">
-        <v>student_case,behavior</v>
+        <v>家庭,安全,student_case</v>
       </c>
       <c r="M2" t="str">
-        <v>SC_S1D2</v>
+        <v>SC_S1D1</v>
       </c>
       <c r="N2" t="str">
-        <v>把模糊印象转成可分析的行为数据</v>
+        <v>E2 为最高安全风险编码（★★★★★），安全永远先于学业和行为</v>
       </c>
       <c r="O2" t="str">
-        <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果；只记录看到的，不写推测和评价；一周后统计最高频的 A 和 C；针对最高频的 A 做一次环境调整并观察变化</v>
+        <v>立即启动学校安全流程，暂停学业干预，优先安全；通知年级组长与德育处，24 小时内完成安全评估与安全计划；通过学校正式渠道启动未成年人保护流程，记录具体信号（只记录不推测）；联系心理总监进行安全评估，家校安全沟通</v>
       </c>
       <c r="P2" t="str">
-        <v>我注意到你最近有些变化，我想先了解你的感受。你可以只说一点点。</v>
+        <v>我理解您的担心。关于 XX 的情况，我们通过学校正规渠道一起来处理，确保孩子的安全是第一位的。</v>
       </c>
       <c r="Q2" t="str">
-        <v>识别出至少一个可干预的诱因</v>
+        <v>24 小时内启动响应；安全风险解除</v>
       </c>
       <c r="R2" t="str">
-        <v>每次 2 分钟</v>
+        <v>立即响应</v>
       </c>
       <c r="S2" t="str">
-        <v>连续 7 天</v>
+        <v>24 小时内完成安全评估</v>
       </c>
       <c r="T2" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U2" t="str">
-        <v>不要在记录中使用诊断性词汇；不要向学生展示记录表</v>
+        <v>不要自行联系家长「了解情况」（可能加重家庭暴力）；不要让学生「证明」受伤（二次伤害）；不要承诺保密；不要自行调查或调解家庭内部事务</v>
       </c>
       <c r="V2" t="str">
         <v/>
@@ -591,31 +591,31 @@
         <v>A</v>
       </c>
       <c r="AA2" t="str">
-        <v>应用行为分析在班级中的实践</v>
+        <v>小学部学生个体问题解决手册 V6.0 / 术语库 V2.0 SA03-SA04</v>
       </c>
       <c r="AB2" t="str">
-        <v>一周内记录 &gt;= 8 次</v>
+        <v/>
       </c>
       <c r="AC2" t="str">
-        <v>一周记录不足 3 次</v>
+        <v>安全风险未解除→持续按红线流程执行，转心理健康中心专业转介</v>
       </c>
       <c r="AD2" t="str">
-        <v>准备记录表</v>
+        <v/>
       </c>
       <c r="AE2" t="str">
-        <v>记录表</v>
+        <v/>
       </c>
       <c r="AF2" t="str">
-        <v>一次执行记录</v>
+        <v>安全事件记录</v>
       </c>
       <c r="AG2" t="str">
         <v/>
       </c>
       <c r="AH2" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AI2" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ2" t="str">
         <v/>
@@ -626,10 +626,10 @@
         <v>SC_RX_02</v>
       </c>
       <c r="B3" t="str">
-        <v>低压力谈话框架</v>
+        <v>亲子紧张家校沟通（E1）</v>
       </c>
       <c r="C3" t="str">
-        <v>低压力谈话框架</v>
+        <v>亲子紧张家校沟通</v>
       </c>
       <c r="D3" t="str">
         <v>student_case</v>
@@ -644,46 +644,46 @@
         <v>teacher</v>
       </c>
       <c r="H3" t="str">
-        <v>学生情绪明显但难以表达时</v>
+        <v>孩子表达对某家长恐惧或不满；家长说「管不了」；在校与家庭行为差异显著</v>
       </c>
       <c r="I3" t="str">
         <v>medium</v>
       </c>
       <c r="J3" t="str">
-        <v>SC_AT_01</v>
+        <v>E1</v>
       </c>
       <c r="K3" t="str">
-        <v>情绪调节困难</v>
+        <v>亲子紧张型</v>
       </c>
       <c r="L3" t="str">
-        <v>student_case,emotion</v>
+        <v>家庭,student_case</v>
       </c>
       <c r="M3" t="str">
-        <v>SC_S1D3</v>
+        <v>SC_S1D6</v>
       </c>
       <c r="N3" t="str">
-        <v>在不施压的前提下建立表达通道</v>
+        <v/>
       </c>
       <c r="O3" t="str">
-        <v>选一个不被打扰、非正式的场合；从一个具体的观察事实开始，不问「你怎么了」；给出选择而非追问：「你可以只说一点点，也可以先不说」；结束时明确下一次可以找你的时间和方式</v>
+        <v>开场陈述观察到的事实而非结论（不做诊断不贴标签）；呈现 2-3 个可选方案供家长选择（给选项，不给任务）；强调「我们一起」，让家长有掌控感和参与感；用心智化话术·家长版沟通，从「纠错模式」切换到「连接模式」</v>
       </c>
       <c r="P3" t="str">
-        <v>我注意到你这两天午休都一个人待着。你可以只说一点点，不需要马上解释清楚。</v>
+        <v>我注意到 XX 最近有些变化——[具体描述 1-2 个客观行为]。我想和您一起了解一下，看看我们各自可以怎么帮他。您方便聊聊吗？</v>
       </c>
       <c r="Q3" t="str">
-        <v>学生愿意做出任何程度的表达</v>
+        <v>家长回应率&gt;80%；学生情绪安全感提升</v>
       </c>
       <c r="R3" t="str">
-        <v>10 分钟</v>
+        <v>15-30 分钟</v>
       </c>
       <c r="S3" t="str">
-        <v>每周一次</v>
+        <v>按需沟通，建立每周固定节奏</v>
       </c>
       <c r="T3" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U3" t="str">
-        <v>不要在其他学生在场时进行；不要承诺保密后又告知他人</v>
+        <v>不在孩子面前批评其家长；不给家长贴「不合格」标签；不在群聊中讨论学生个人情况；不替孩子「告密」也不帮孩子「隐瞒」</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -698,34 +698,34 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AA3" t="str">
-        <v>学生个体支持手册 第3章</v>
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 E1 / ⑨ 家校沟通处方）</v>
       </c>
       <c r="AB3" t="str">
-        <v>学生做出回应（包括沉默但未回避）</v>
+        <v/>
       </c>
       <c r="AC3" t="str">
-        <v>连续两次学生完全回避</v>
+        <v>家长拒绝沟通→改用书面+给选项模式；关系持续恶化→启动 E2 评估</v>
       </c>
       <c r="AD3" t="str">
-        <v>准备记录表</v>
+        <v/>
       </c>
       <c r="AE3" t="str">
-        <v>记录表</v>
+        <v/>
       </c>
       <c r="AF3" t="str">
-        <v>一次执行记录</v>
+        <v/>
       </c>
       <c r="AG3" t="str">
         <v/>
       </c>
       <c r="AH3" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AI3" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ3" t="str">
         <v/>
@@ -736,10 +736,10 @@
         <v>SC_RX_03</v>
       </c>
       <c r="B4" t="str">
-        <v>同伴联结重建方案</v>
+        <v>三步行为契约·攻击冲动（B3）</v>
       </c>
       <c r="C4" t="str">
-        <v>同伴联结重建方案</v>
+        <v>三步行为契约·攻</v>
       </c>
       <c r="D4" t="str">
         <v>student_case</v>
@@ -754,46 +754,46 @@
         <v>teacher</v>
       </c>
       <c r="H4" t="str">
-        <v>学生被孤立或同伴冲突反复发生</v>
+        <v>周内发生肢体冲突；常说伤人的话；冲动控制明显弱于同龄</v>
       </c>
       <c r="I4" t="str">
         <v>medium</v>
       </c>
       <c r="J4" t="str">
-        <v>SC_AT_03</v>
+        <v>B3</v>
       </c>
       <c r="K4" t="str">
-        <v>同伴关系受损</v>
+        <v>攻击冲动型</v>
       </c>
       <c r="L4" t="str">
-        <v>student_case,social</v>
+        <v>行为,student_case</v>
       </c>
       <c r="M4" t="str">
-        <v>SC_S1D4</v>
+        <v>SC_S1D3</v>
       </c>
       <c r="N4" t="str">
-        <v>通过结构化任务重建同伴关系</v>
+        <v/>
       </c>
       <c r="O4" t="str">
-        <v>找一个该学生擅长的领域，设计一个需要合作的小任务；为其匹配一到两位关系中性的同学；任务完成后公开肯定该学生的具体贡献；两周后观察自然互动是否增加</v>
+        <v>共定目标：具体可测（如「老师叫我名字时我能站起来」而非「认真听讲」）；明确奖励：首选社会性奖励（自由时间/当小助手/优先选择权），物质奖励辅助；每日复盘：放学 30 秒复盘——做到了吗？为什么？明天怎么调整？；依恋增强版：增加关系目标——「当你沮丧或想发火时，可以来找我，我们一起想办法」</v>
       </c>
       <c r="P4" t="str">
-        <v>这件事你最在行，你带着他们两个一起弄，周五给大家看看。</v>
+        <v>这一周，当你感到沮丧或想发火时，可以来找我，我们一起想办法。你愿意来找我，这本身就是最大的进步。</v>
       </c>
       <c r="Q4" t="str">
-        <v>自然互动频次增加</v>
+        <v>1 周目标达标率&gt;60%；2 周&gt;80%；冲突频率下降</v>
       </c>
       <c r="R4" t="str">
-        <v>一周</v>
+        <v>5 分钟</v>
       </c>
       <c r="S4" t="str">
-        <v>每两周一轮</v>
+        <v>2 周一个周期</v>
       </c>
       <c r="T4" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U4" t="str">
-        <v>不要公开点明该学生「需要帮助」</v>
+        <v>不要在冲突过程中训斥（高唤醒状态下训斥无效）；不要当众羞辱；目标必须具体可测</v>
       </c>
       <c r="V4" t="str">
         <v/>
@@ -808,34 +808,34 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AA4" t="str">
-        <v>同伴关系干预实务</v>
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 B3 / ② 技术详解卡 T4）</v>
       </c>
       <c r="AB4" t="str">
-        <v>两周内出现自发互动</v>
+        <v/>
       </c>
       <c r="AC4" t="str">
-        <v>两轮后无变化（升级至 L2）</v>
+        <v>ABC 分析回溯触发原因；目标再分小一半；体动优势→运动释放能量替代攻击</v>
       </c>
       <c r="AD4" t="str">
-        <v>准备记录表</v>
+        <v/>
       </c>
       <c r="AE4" t="str">
-        <v>记录表</v>
+        <v/>
       </c>
       <c r="AF4" t="str">
-        <v>一次执行记录</v>
+        <v/>
       </c>
       <c r="AG4" t="str">
         <v/>
       </c>
       <c r="AH4" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AI4" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ4" t="str">
         <v/>
@@ -846,16 +846,16 @@
         <v>SC_RX_04</v>
       </c>
       <c r="B5" t="str">
-        <v>三级支持决策卡</v>
+        <v>注意力分散干预处方（A1）</v>
       </c>
       <c r="C5" t="str">
-        <v>三级支持决策卡</v>
+        <v>注意力分散干预处</v>
       </c>
       <c r="D5" t="str">
         <v>student_case</v>
       </c>
       <c r="E5" t="str">
-        <v>checklist</v>
+        <v>framework</v>
       </c>
       <c r="F5" t="str">
         <v>all</v>
@@ -864,46 +864,46 @@
         <v>teacher</v>
       </c>
       <c r="H5" t="str">
-        <v>需要判断由教师支持、年级协同还是专业会商</v>
+        <v>月内教师多次提醒；作业完成时间远超同龄；课堂切换需反复提醒</v>
       </c>
       <c r="I5" t="str">
-        <v>high</v>
+        <v>low</v>
       </c>
       <c r="J5" t="str">
-        <v>SC_AT_05</v>
+        <v>A1</v>
       </c>
       <c r="K5" t="str">
-        <v>适应障碍信号</v>
+        <v>注意力分散型</v>
       </c>
       <c r="L5" t="str">
-        <v>student_case,adapt,crisis</v>
+        <v>学习,student_case</v>
       </c>
       <c r="M5" t="str">
-        <v>SC_S1D5</v>
+        <v>SC_S1D2</v>
       </c>
       <c r="N5" t="str">
-        <v>让支持层级的判断有据可依</v>
+        <v/>
       </c>
       <c r="O5" t="str">
-        <v>整理问题的起止时间线和关键事件；列出已尝试的支持措施和各自效果；对照三级标准判断当前层级；按层级准备对应材料并启动流程</v>
+        <v>关系锚定（约 30 秒）：蹲下平视——「我就在旁边，做完这一段你可以随时来找我核对」；把任务分成 5-10 分钟小段，每段一个明确目标；用可视化定时器倒计时，完成一段休息 2 分钟，3 段=较大奖励；叠加 T2 注意力信号约定：私下约定暗号，走神时用暗号提醒不做语言批评</v>
       </c>
       <c r="P5" t="str">
-        <v>目前我们先基于观察事实协同支持，不做标签判断，重点是看哪些支持对学生有效。</v>
+        <v>这个暗号是我们俩之间的小秘密——它代表「我知道你在努力，我看到了」。</v>
       </c>
       <c r="Q5" t="str">
-        <v>形成一份可交接的支持材料</v>
+        <v>1 周作业效率改善；1-2 周走神次数显著下降</v>
       </c>
       <c r="R5" t="str">
-        <v>30 分钟</v>
+        <v>5-10 分钟/段</v>
       </c>
       <c r="S5" t="str">
-        <v>每次层级变化时</v>
+        <v>每天×2 周</v>
       </c>
       <c r="T5" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U5" t="str">
-        <v>不得在材料中写入诊断性结论</v>
+        <v>奖励首选社会性奖励（自由时间/当小助手），物质奖励辅助；定时器必须可视化；暗号必须非惩罚性</v>
       </c>
       <c r="V5" t="str">
         <v/>
@@ -921,31 +921,31 @@
         <v>A</v>
       </c>
       <c r="AA5" t="str">
-        <v>学生个体支持手册 第6章</v>
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 A1 / ② 技术详解卡 T1-T2）</v>
       </c>
       <c r="AB5" t="str">
-        <v>材料包含时间线、措施和效果三部分</v>
+        <v/>
       </c>
       <c r="AC5" t="str">
-        <v>无法回忆已尝试过哪些措施</v>
+        <v>段长缩短至 3 分钟甚至 1 分钟；确认是否难度超载→先降任务难度</v>
       </c>
       <c r="AD5" t="str">
-        <v>准备记录表</v>
+        <v/>
       </c>
       <c r="AE5" t="str">
-        <v>记录表</v>
+        <v/>
       </c>
       <c r="AF5" t="str">
-        <v>一次执行记录</v>
+        <v/>
       </c>
       <c r="AG5" t="str">
         <v/>
       </c>
       <c r="AH5" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AI5" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ5" t="str">
         <v/>
@@ -956,16 +956,16 @@
         <v>SC_RX_05</v>
       </c>
       <c r="B6" t="str">
-        <v>学业交叉评估转介单</v>
+        <v>动机缺失干预处方（A2）</v>
       </c>
       <c r="C6" t="str">
-        <v>学业交叉评估转介</v>
+        <v>动机缺失干预处方</v>
       </c>
       <c r="D6" t="str">
         <v>student_case</v>
       </c>
       <c r="E6" t="str">
-        <v>checklist</v>
+        <v>framework</v>
       </c>
       <c r="F6" t="str">
         <v>all</v>
@@ -974,46 +974,46 @@
         <v>teacher</v>
       </c>
       <c r="H6" t="str">
-        <v>学业下降是最突出的表现时</v>
+        <v>成功失败均无明显情绪；需反复催促才开始；不主动不求助不逃避</v>
       </c>
       <c r="I6" t="str">
         <v>low</v>
       </c>
       <c r="J6" t="str">
-        <v>SC_AT_04</v>
+        <v>A2</v>
       </c>
       <c r="K6" t="str">
-        <v>学业功能下降</v>
+        <v>动机缺失型</v>
       </c>
       <c r="L6" t="str">
-        <v>student_case,academic</v>
+        <v>学习,student_case</v>
       </c>
       <c r="M6" t="str">
-        <v>SC_S1D1</v>
+        <v>SC_S1D2</v>
       </c>
       <c r="N6" t="str">
-        <v>把学业问题转到学习问题模块做精准诊断</v>
+        <v/>
       </c>
       <c r="O6" t="str">
-        <v>确认学业下降已持续四周以上；记录哪些科目、哪些环节受影响最明显；在学习问题模块完成三层诊断；按三层诊断结果匹配教学支架</v>
+        <v>优势定位：调取优势测评 Top2-3 类型（未测评→安排测评或教师观察法）；优势-问题匹配：用优势通道激活学习动机（如身体动觉型→运动间歇奖励）；叠加 T4 三步行为契约（动机版）：共定目标+社会性奖励+每日复盘；2 周评估：优势通道是否奏效，无效则复查定位或调整匹配路径</v>
       </c>
       <c r="P6" t="str">
-        <v>我们关注的不只是分数，而是他在学习过程中遇到了什么困难。</v>
+        <v>我想和你一起发现你的优点——不是因为你有问题要改正，而是因为我想更多了解你好的那一面。</v>
       </c>
       <c r="Q6" t="str">
-        <v>定位到行为、认知或关系层面的具体卡点</v>
+        <v>通过优势通道激活学习动机；2 周内出现主动行为</v>
       </c>
       <c r="R6" t="str">
         <v>15 分钟</v>
       </c>
       <c r="S6" t="str">
-        <v>按需</v>
+        <v>持续，2 周验证优势假设</v>
       </c>
       <c r="T6" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U6" t="str">
-        <v>不要在未做三层诊断前直接安排补课</v>
+        <v>不把「懒」「不上进」当标签贴给学生；避免纯补偿式「缺啥补啥」干预</v>
       </c>
       <c r="V6" t="str">
         <v/>
@@ -1028,34 +1028,34 @@
         <v/>
       </c>
       <c r="Z6" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="AA6" t="str">
-        <v>跨模块协同指引</v>
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 A2）</v>
       </c>
       <c r="AB6" t="str">
-        <v>完成学习问题模块的三层诊断</v>
+        <v/>
       </c>
       <c r="AC6" t="str">
-        <v>诊断结果无明确主导层面</v>
+        <v>优势定位可能不准→复查测评或观察；任务难度与优势通道不匹配→调整匹配路径</v>
       </c>
       <c r="AD6" t="str">
-        <v>准备记录表</v>
+        <v/>
       </c>
       <c r="AE6" t="str">
-        <v>记录表</v>
+        <v/>
       </c>
       <c r="AF6" t="str">
-        <v>一次执行记录</v>
+        <v/>
       </c>
       <c r="AG6" t="str">
         <v/>
       </c>
       <c r="AH6" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AI6" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ6" t="str">
         <v/>
@@ -1066,16 +1066,16 @@
         <v>SC_RX_06</v>
       </c>
       <c r="B7" t="str">
-        <v>危机转介操作卡</v>
+        <v>技能不足干预处方（A3）</v>
       </c>
       <c r="C7" t="str">
-        <v>危机转介操作卡</v>
+        <v>技能不足干预处方</v>
       </c>
       <c r="D7" t="str">
         <v>student_case</v>
       </c>
       <c r="E7" t="str">
-        <v>checklist</v>
+        <v>framework</v>
       </c>
       <c r="F7" t="str">
         <v>all</v>
@@ -1084,46 +1084,46 @@
         <v>teacher</v>
       </c>
       <c r="H7" t="str">
-        <v>出现拒学、躯体化或自伤相关信号</v>
+        <v>某科持续低于 75 分；基础技能落后；已努力但效果不佳；非广泛性</v>
       </c>
       <c r="I7" t="str">
-        <v>crisis</v>
+        <v>low</v>
       </c>
       <c r="J7" t="str">
-        <v>SC_AT_05</v>
+        <v>A3</v>
       </c>
       <c r="K7" t="str">
-        <v>适应障碍信号</v>
+        <v>技能不足型</v>
       </c>
       <c r="L7" t="str">
-        <v>student_case,adapt,crisis</v>
+        <v>学习,student_case</v>
       </c>
       <c r="M7" t="str">
-        <v>SC_S1D5</v>
+        <v>SC_S1D2</v>
       </c>
       <c r="N7" t="str">
-        <v>确保危机情形被专业力量及时接住</v>
+        <v/>
       </c>
       <c r="O7" t="str">
-        <v>确保学生当下处于安全环境并有人陪伴；立即联系校内心理专员，说明观察到的具体事实；同步通知年级组长和家长；完整记录时间线，不做任何诊断性表述</v>
+        <v>确认是否学科基础技能落后（识字量/计算能力/学习方法）；优势锚定学习策略：空间型→思维导图，逻辑型→归纳分析；降任务难度分级：从当前水平+1 级开始，小步胜利；叠加 T3 渐进参与计划（学业版）逐步建立学习信心</v>
       </c>
       <c r="P7" t="str">
-        <v>我现在需要请专业老师一起来看看，我会一直陪着你。</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
-        <v>在 24 小时内建立专业支持连接</v>
+        <v>4 周内薄弱科目出现改善迹象</v>
       </c>
       <c r="R7" t="str">
-        <v>立即</v>
+        <v/>
       </c>
       <c r="S7" t="str">
-        <v>按需</v>
+        <v/>
       </c>
       <c r="T7" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="U7" t="str">
-        <v>严禁班主任自行判断风险等级；严禁延迟上报；严禁在学生面前讨论转介</v>
+        <v>不用于替代危机处置</v>
       </c>
       <c r="V7" t="str">
         <v/>
@@ -1141,46 +1141,2796 @@
         <v>A</v>
       </c>
       <c r="AA7" t="str">
-        <v>校园心理危机干预规范</v>
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 A3）</v>
       </c>
       <c r="AB7" t="str">
-        <v>2 小时内完成专员联系</v>
+        <v/>
       </c>
       <c r="AC7" t="str">
-        <v>超过 24 小时未建立联系</v>
+        <v>降任务难度分级→从当前水平+1 级开始；空间型优势→思维导图学习法</v>
       </c>
       <c r="AD7" t="str">
-        <v>准备记录表</v>
+        <v/>
       </c>
       <c r="AE7" t="str">
-        <v>记录表</v>
+        <v/>
       </c>
       <c r="AF7" t="str">
-        <v>一次执行记录</v>
+        <v/>
       </c>
       <c r="AG7" t="str">
         <v/>
       </c>
       <c r="AH7" t="str">
-        <v>学生个体问题手册v1</v>
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
       </c>
       <c r="AI7" t="str">
-        <v>4.0.0</v>
+        <v>4.5.0</v>
       </c>
       <c r="AJ7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SC_RX_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>课堂纪律干预处方（B1）</v>
+      </c>
+      <c r="C8" t="str">
+        <v>课堂纪律干预处方</v>
+      </c>
+      <c r="D8" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E8" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F8" t="str">
+        <v>all</v>
+      </c>
+      <c r="G8" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H8" t="str">
+        <v>每日被点名提醒多次；行为影响其他同学；对指令选择性听从</v>
+      </c>
+      <c r="I8" t="str">
+        <v>low</v>
+      </c>
+      <c r="J8" t="str">
+        <v>B1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>课堂纪律型</v>
+      </c>
+      <c r="L8" t="str">
+        <v>行为,student_case</v>
+      </c>
+      <c r="M8" t="str">
+        <v>SC_S1D3</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v>T4 三步行为契约：共定具体可测目标（如「前 15 分钟不讲话」）；明确社会性奖励，低年段当日兑现、高年段延迟至周末；每日复盘 30 秒，记录达标情况；叠加 T2 注意力信号约定，减少语言批评</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>1 周目标达标率&gt;60%；课堂干扰减少</v>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V8" t="str">
+        <v/>
+      </c>
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+      <c r="Z8" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 B1）</v>
+      </c>
+      <c r="AB8" t="str">
+        <v/>
+      </c>
+      <c r="AC8" t="str">
+        <v>目标再分小一半；问孩子「你想要什么奖励」；ABC 分析回溯</v>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>SC_RX_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>规则习惯干预处方（B2）</v>
+      </c>
+      <c r="C9" t="str">
+        <v>规则习惯干预处方</v>
+      </c>
+      <c r="D9" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E9" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F9" t="str">
+        <v>all</v>
+      </c>
+      <c r="G9" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H9" t="str">
+        <v>作业经常不交/潦草；物品整理混乱常丢东西；时间概念弱常迟到</v>
+      </c>
+      <c r="I9" t="str">
+        <v>low</v>
+      </c>
+      <c r="J9" t="str">
+        <v>B2</v>
+      </c>
+      <c r="K9" t="str">
+        <v>规则习惯型</v>
+      </c>
+      <c r="L9" t="str">
+        <v>行为,student_case</v>
+      </c>
+      <c r="M9" t="str">
+        <v>SC_S1D3</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v>T4 三步行为契约：从最易改变的习惯入手（如「一课桌」整理）；优势锚定量化版：逻辑型→计分系统、图表追踪；动觉型→动作化规则；每日复盘+每周奖励；2 周评估达标率，持续调整目标粒度</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v>1 周目标达标率&gt;60%；2 周&gt;80%</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V9" t="str">
+        <v/>
+      </c>
+      <c r="W9" t="str">
+        <v/>
+      </c>
+      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
+        <v/>
+      </c>
+      <c r="Z9" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 B2）</v>
+      </c>
+      <c r="AB9" t="str">
+        <v/>
+      </c>
+      <c r="AC9" t="str">
+        <v>从物品整理入手→从「一课桌」开始；逻辑型优势→用计分系统、图表追踪</v>
+      </c>
+      <c r="AD9" t="str">
+        <v/>
+      </c>
+      <c r="AE9" t="str">
+        <v/>
+      </c>
+      <c r="AF9" t="str">
+        <v/>
+      </c>
+      <c r="AG9" t="str">
+        <v/>
+      </c>
+      <c r="AH9" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SC_RX_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>情绪调节干预处方（C2）</v>
+      </c>
+      <c r="C10" t="str">
+        <v>情绪调节干预处方</v>
+      </c>
+      <c r="D10" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E10" t="str">
+        <v>script</v>
+      </c>
+      <c r="F10" t="str">
+        <v>all</v>
+      </c>
+      <c r="G10" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H10" t="str">
+        <v>周内多次强烈情绪；平复时间远超同龄；情绪后伴随后悔自责</v>
+      </c>
+      <c r="I10" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J10" t="str">
+        <v>C2</v>
+      </c>
+      <c r="K10" t="str">
+        <v>情绪调节型</v>
+      </c>
+      <c r="L10" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="M10" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v>T7 情绪命名与接纳：命名情绪（「我看到你拳头攥得很紧，是叫「生气」吗？」）；无条件接纳：「谢谢你告诉我。生气或难过是正常的，每个人都会有。」；情绪平复后才进入问题解决；叠加 T12 心智化回应完整版，情绪升级时「不撑不退」保持稳定</v>
+      </c>
+      <c r="P10" t="str">
+        <v>无论你是因为什么有这种感觉，你都可以告诉我。有情绪是正常的，我在这里陪着你。</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>即时降低情绪强度；2-4 周开始用语言表达情绪</v>
+      </c>
+      <c r="R10" t="str">
+        <v>3-5 分钟</v>
+      </c>
+      <c r="S10" t="str">
+        <v>即时/按需</v>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v>接纳的是情绪，规范的是行为——「你可以生气，但不可以打人」；不要在情绪爆发时讲道理</v>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 C2）</v>
+      </c>
+      <c r="AB10" t="str">
+        <v/>
+      </c>
+      <c r="AC10" t="str">
+        <v>孩子说不出情绪→提供 2-3 选项；情绪升级而不平复→不撑不退保持稳定</v>
+      </c>
+      <c r="AD10" t="str">
+        <v/>
+      </c>
+      <c r="AE10" t="str">
+        <v/>
+      </c>
+      <c r="AF10" t="str">
+        <v/>
+      </c>
+      <c r="AG10" t="str">
+        <v/>
+      </c>
+      <c r="AH10" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>SC_RX_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>焦虑退缩干预处方（C1）</v>
+      </c>
+      <c r="C11" t="str">
+        <v>焦虑退缩干预处方</v>
+      </c>
+      <c r="D11" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E11" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F11" t="str">
+        <v>all</v>
+      </c>
+      <c r="G11" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H11" t="str">
+        <v>从不/极少主动举手；被点名时明显紧张；回避展示场合；常说「我害怕」</v>
+      </c>
+      <c r="I11" t="str">
+        <v>low</v>
+      </c>
+      <c r="J11" t="str">
+        <v>C1</v>
+      </c>
+      <c r="K11" t="str">
+        <v>焦虑退缩型</v>
+      </c>
+      <c r="L11" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="M11" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v>T3 渐进参与计划：安全基地启动（1-2 分钟非学习闲聊）；第 1 周：老师看向你时保持目光接触；第 2-3 周：心里说答案→对同桌小声说；第 4 周：举手一次（事先约定，老师会叫你）；叠加 T8 优势发现日记积累成功体验</v>
+      </c>
+      <c r="P11" t="str">
+        <v>放轻松，我们只是练习，不是考试。</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>4 周内实现首次举手</v>
+      </c>
+      <c r="R11" t="str">
+        <v>即时</v>
+      </c>
+      <c r="S11" t="str">
+        <v>4 周渐进</v>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v>前两周重点不是「行为达标」而是「建立安全感」；不强迫发言</v>
+      </c>
+      <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
+      </c>
+      <c r="Z11" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 C1 / ② 技术详解卡 T3）</v>
+      </c>
+      <c r="AB11" t="str">
+        <v/>
+      </c>
+      <c r="AC11" t="str">
+        <v>某阶段停滞&gt;2 周→退回上阶段重建信心；检查环境安全（被嘲笑等）</v>
+      </c>
+      <c r="AD11" t="str">
+        <v/>
+      </c>
+      <c r="AE11" t="str">
+        <v/>
+      </c>
+      <c r="AF11" t="str">
+        <v/>
+      </c>
+      <c r="AG11" t="str">
+        <v/>
+      </c>
+      <c r="AH11" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>SC_RX_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>低自尊干预处方（C3）</v>
+      </c>
+      <c r="C12" t="str">
+        <v>低自尊干预处方（</v>
+      </c>
+      <c r="D12" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E12" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F12" t="str">
+        <v>all</v>
+      </c>
+      <c r="G12" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H12" t="str">
+        <v>常说「我不行」「我笨」；拒绝尝试能力范围内的事；对批评异常敏感</v>
+      </c>
+      <c r="I12" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J12" t="str">
+        <v>C3</v>
+      </c>
+      <c r="K12" t="str">
+        <v>低自尊型</v>
+      </c>
+      <c r="L12" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="M12" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v>关系预热：「我想和你一起发现你的优点——不是因为你做错了什么」；T8 优势发现日记：每天找 1-2 件「今天做得不错的事」，具体到行为、优先优势领域；累计一周班会上公开肯定（「本周 XX 之星」形式）；连续 4 周后让学生自己写，老师逐步退出；叠加 T11 优势锚定法持续强化</v>
+      </c>
+      <c r="P12" t="str">
+        <v>我注意到你今天把笔借给了同桌，这叫乐于助人——这是你的优点。</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>4 周后自我否定语言明显减少</v>
+      </c>
+      <c r="R12" t="str">
+        <v>5 分钟</v>
+      </c>
+      <c r="S12" t="str">
+        <v>4 周</v>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v>避免模糊的「你很棒」（会被不安全依恋学生过滤为安慰）；不要在公开场合与别人比较</v>
+      </c>
+      <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <v/>
+      </c>
+      <c r="Z12" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 C3 / ② 技术详解卡 T6）</v>
+      </c>
+      <c r="AB12" t="str">
+        <v/>
+      </c>
+      <c r="AC12" t="str">
+        <v>找不出优点→老师说「今天你做的最小一件好事」；全科失败→从非学业优势领域找</v>
+      </c>
+      <c r="AD12" t="str">
+        <v/>
+      </c>
+      <c r="AE12" t="str">
+        <v/>
+      </c>
+      <c r="AF12" t="str">
+        <v/>
+      </c>
+      <c r="AG12" t="str">
+        <v/>
+      </c>
+      <c r="AH12" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI12" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>SC_RX_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>同伴冲突干预处方（D1）</v>
+      </c>
+      <c r="C13" t="str">
+        <v>同伴冲突干预处方</v>
+      </c>
+      <c r="D13" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E13" t="str">
+        <v>script</v>
+      </c>
+      <c r="F13" t="str">
+        <v>all</v>
+      </c>
+      <c r="G13" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H13" t="str">
+        <v>每周处理该生同伴纠纷多次；同伴提名中处于被排斥位置</v>
+      </c>
+      <c r="I13" t="str">
+        <v>low</v>
+      </c>
+      <c r="J13" t="str">
+        <v>D1</v>
+      </c>
+      <c r="K13" t="str">
+        <v>同伴冲突型</v>
+      </c>
+      <c r="L13" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="M13" t="str">
+        <v>SC_S1D5</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>T12 冲突调解三步心智化：先各说一句「我觉得……」；听完后把对方的话重述一遍（理解他人心理状态）；连接需求：「除了打架，还有什么办法？」；叠加 T4 行为契约（社交版）：约定替代行为并正强化</v>
+      </c>
+      <c r="P13" t="str">
+        <v>你们俩现在都很生气。先各说一句「我觉得……」好吗？……除了打架，还有什么办法？</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>2 周内冲突频率下降</v>
+      </c>
+      <c r="R13" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S13" t="str">
+        <v>2 周一个周期</v>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v>不做「法官模式」判断对错；不当众点名批评</v>
+      </c>
+      <c r="V13" t="str">
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
+        <v/>
+      </c>
+      <c r="Z13" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 D1 / ⑦ 心智化话术库）</v>
+      </c>
+      <c r="AB13" t="str">
+        <v/>
+      </c>
+      <c r="AC13" t="str">
+        <v>同伴不匹配→换人；双方都退缩→改为三人小组</v>
+      </c>
+      <c r="AD13" t="str">
+        <v/>
+      </c>
+      <c r="AE13" t="str">
+        <v/>
+      </c>
+      <c r="AF13" t="str">
+        <v/>
+      </c>
+      <c r="AG13" t="str">
+        <v/>
+      </c>
+      <c r="AH13" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI13" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>SC_RX_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>社交退缩干预处方（D2）</v>
+      </c>
+      <c r="C14" t="str">
+        <v>社交退缩干预处方</v>
+      </c>
+      <c r="D14" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E14" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F14" t="str">
+        <v>all</v>
+      </c>
+      <c r="G14" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H14" t="str">
+        <v>自由活动时通常独自一人；小组活动被动参与；自述「没朋友」</v>
+      </c>
+      <c r="I14" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J14" t="str">
+        <v>D2</v>
+      </c>
+      <c r="K14" t="str">
+        <v>社交退缩型</v>
+      </c>
+      <c r="L14" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="M14" t="str">
+        <v>SC_S1D5</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>T10 友谊桥同伴配对：安排温和、社交能力中等的同伴（不选最强的）；设计需两人协作的任务，从任务互动过渡到社交互动；每周末分别问双方感受，关注同伴心理状态；叠加 T9 社交剧本练习降低社交启动难度</v>
+      </c>
+      <c r="P14" t="str">
+        <v>XX 同学需要一个朋友，我想请你帮忙——因为你是我见过最温和、最让人放心的同学。这不是任务，是邀请——你愿意试试看吗？</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>4 周内自由活动出现固定玩伴</v>
+      </c>
+      <c r="R14" t="str">
+        <v>持续</v>
+      </c>
+      <c r="S14" t="str">
+        <v>4 周</v>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v>不选最强的同伴（碾压式配对适得其反）；不要忽视同伴心理状态（防止同伴耗竭）</v>
+      </c>
+      <c r="V14" t="str">
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
+      </c>
+      <c r="Z14" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 D2 / ② 技术详解卡 T8）</v>
+      </c>
+      <c r="AB14" t="str">
+        <v/>
+      </c>
+      <c r="AC14" t="str">
+        <v>同伴不匹配→换人（关键：互补而不碾压）；两人都退缩→三人小组降低压力</v>
+      </c>
+      <c r="AD14" t="str">
+        <v/>
+      </c>
+      <c r="AE14" t="str">
+        <v/>
+      </c>
+      <c r="AF14" t="str">
+        <v/>
+      </c>
+      <c r="AG14" t="str">
+        <v/>
+      </c>
+      <c r="AH14" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>SC_RX_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>社交技能缺失干预处方（D3）</v>
+      </c>
+      <c r="C15" t="str">
+        <v>社交技能缺失干预</v>
+      </c>
+      <c r="D15" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E15" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F15" t="str">
+        <v>all</v>
+      </c>
+      <c r="G15" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H15" t="str">
+        <v>不会用恰当方式加入游戏；不知轮流分享规则；读不懂同伴表情和语气</v>
+      </c>
+      <c r="I15" t="str">
+        <v>low</v>
+      </c>
+      <c r="J15" t="str">
+        <v>D3</v>
+      </c>
+      <c r="K15" t="str">
+        <v>技能缺失型</v>
+      </c>
+      <c r="L15" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="M15" t="str">
+        <v>SC_S1D5</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v>T9 社交剧本练习：安全基地预热（1-2 分钟轻松对话）；设计简短社交剧本（走近小组站 30 秒→等停顿→说「我可以加入吗」）；老师示范→学生练习 3 遍；真实场景观察使用情况，当天反馈；叠加 T10 友谊桥提供实践场</v>
+      </c>
+      <c r="P15" t="str">
+        <v>放轻松，我们只是练习不是考试。</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>2 周内开始尝试在真实场景中使用剧本行为</v>
+      </c>
+      <c r="R15" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S15" t="str">
+        <v>2 周</v>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v>安全基地预热不是浪费时间——焦虑状态下的练习是「表演」，安全状态下的才是「内化」</v>
+      </c>
+      <c r="V15" t="str">
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <v/>
+      </c>
+      <c r="Z15" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 D3 / ② 技术详解卡 T7）</v>
+      </c>
+      <c r="AB15" t="str">
+        <v/>
+      </c>
+      <c r="AC15" t="str">
+        <v>记不住台词→缩减为一个核心句；不敢用→先小范围练习（同桌）</v>
+      </c>
+      <c r="AD15" t="str">
+        <v/>
+      </c>
+      <c r="AE15" t="str">
+        <v/>
+      </c>
+      <c r="AF15" t="str">
+        <v/>
+      </c>
+      <c r="AG15" t="str">
+        <v/>
+      </c>
+      <c r="AH15" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI15" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SC_RX_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>支持缺位干预处方（E3）</v>
+      </c>
+      <c r="C16" t="str">
+        <v>支持缺位干预处方</v>
+      </c>
+      <c r="D16" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E16" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F16" t="str">
+        <v>all</v>
+      </c>
+      <c r="G16" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H16" t="str">
+        <v>主要养育者缺席或频繁更换；家庭经济压力影响生活；家长明确表示无力配合</v>
+      </c>
+      <c r="I16" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J16" t="str">
+        <v>E3</v>
+      </c>
+      <c r="K16" t="str">
+        <v>支持缺位型</v>
+      </c>
+      <c r="L16" t="str">
+        <v>家庭,student_case</v>
+      </c>
+      <c r="M16" t="str">
+        <v>SC_S1D6</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v>T11 优势锚定法（独立·S0 发展）：调取优势测评 Top2-3 类型；以学校为安全基地：建立稳定可预测的师生关系；为优势领域制定 2-3 个学期发展目标，定期跟踪；叠加 T8 优势发现日记积累成功体验；定期 Q06 月度追踪</v>
+      </c>
+      <c r="P16" t="str">
+        <v>你在这里是安全的，你可以自由探索。我不会侵入你的空间，但我一直在这里。</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>以学校为安全基地；优势领域持续发展</v>
+      </c>
+      <c r="R16" t="str">
+        <v>15 分钟</v>
+      </c>
+      <c r="S16" t="str">
+        <v>持续（以月为单位）</v>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v>不替代家庭做「家庭调解」；不以怜悯或同情姿态对待学生</v>
+      </c>
+      <c r="V16" t="str">
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
+        <v/>
+      </c>
+      <c r="Z16" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 E3）</v>
+      </c>
+      <c r="AB16" t="str">
+        <v/>
+      </c>
+      <c r="AC16" t="str">
+        <v>通过 S0 优势发展路径替代补偿家庭支持缺失；定期 Q06 月度追踪</v>
+      </c>
+      <c r="AD16" t="str">
+        <v/>
+      </c>
+      <c r="AE16" t="str">
+        <v/>
+      </c>
+      <c r="AF16" t="str">
+        <v/>
+      </c>
+      <c r="AG16" t="str">
+        <v/>
+      </c>
+      <c r="AH16" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SC_RX_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>优势发展通道（S0）</v>
+      </c>
+      <c r="C17" t="str">
+        <v>优势发展通道（S</v>
+      </c>
+      <c r="D17" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E17" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F17" t="str">
+        <v>all</v>
+      </c>
+      <c r="G17" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H17" t="str">
+        <v>五维筛查零标记 + 六维评估全 A/B + 学有余力（或超前发展特征）</v>
+      </c>
+      <c r="I17" t="str">
+        <v>low</v>
+      </c>
+      <c r="J17" t="str">
+        <v>A3</v>
+      </c>
+      <c r="K17" t="str">
+        <v>技能不足型</v>
+      </c>
+      <c r="L17" t="str">
+        <v>学习,student_case</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v>S0 是独立路径，不与 S1-S5 连通；两条路径可交替不可并行</v>
+      </c>
+      <c r="O17" t="str">
+        <v>S0a 识别：确认五维零标记+六维全 A/B+学有余力特征（10 分钟）；S0b 优势定位：调取优势测评 Top2-3 类型（1-2 年级 50 题版/3-6 年级 20 题版）；S0c 方案制定：T11 独立模式，为每个优势制定 2-3 个学期发展目标，填入优二代成长规划；S0d 月度追踪：每月 Q06 自我探索问卷，关注自我实现和自我升级维度；每学期末复查五维筛查，出现标记→正常转入 S1-S5</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v>优势领域稳步拓展；自我实现/自我升级维度持续上升</v>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V17" t="str">
+        <v/>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
+        <v/>
+      </c>
+      <c r="Z17" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>术语库 V2.0（08 S0-S5 诊疗流程）/ 小学部学生个体问题解决手册 V6.0</v>
+      </c>
+      <c r="AB17" t="str">
+        <v/>
+      </c>
+      <c r="AC17" t="str">
+        <v>学期末复查出现五维筛查标记→转入 S1-S5 流程</v>
+      </c>
+      <c r="AD17" t="str">
+        <v/>
+      </c>
+      <c r="AE17" t="str">
+        <v/>
+      </c>
+      <c r="AF17" t="str">
+        <v/>
+      </c>
+      <c r="AG17" t="str">
+        <v/>
+      </c>
+      <c r="AH17" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SC_RX_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>班级情绪安全感建设（班级氛围）</v>
+      </c>
+      <c r="C18" t="str">
+        <v>班级情绪安全感建</v>
+      </c>
+      <c r="D18" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E18" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F18" t="str">
+        <v>all</v>
+      </c>
+      <c r="G18" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H18" t="str">
+        <v>班级整体情绪安全感偏低；班主任精力透支</v>
+      </c>
+      <c r="I18" t="str">
+        <v>low</v>
+      </c>
+      <c r="J18" t="str">
+        <v>C2;C1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>情绪调节型;焦虑退缩型</v>
+      </c>
+      <c r="L18" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="M18" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v>T12 班级层面心智化：每天 1 次「情绪天气」（晴天/多云/小雨/雷雨，30 秒，不点名不追问）；冲突调解三步心智化（看见情绪→理解他人→连接需求）；教师自我心智化复盘：教师稳定本身就是最强的情绪调节信号</v>
+      </c>
+      <c r="P18" t="str">
+        <v>让情绪表达成为班级常态——当情绪表达是「正常的事」，学生才更容易在需要时说出真实情绪。</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>班级情绪表达常态化；冲突中自发使用心智化语言</v>
+      </c>
+      <c r="R18" t="str">
+        <v>每天 30 秒</v>
+      </c>
+      <c r="S18" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v>情绪天气不是筛查工具，不点名不追问；不在全班面前讨论个别学生</v>
+      </c>
+      <c r="V18" t="str">
+        <v/>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
+        <v/>
+      </c>
+      <c r="Z18" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 班级氛围 / ⑦ 心智化话术库）</v>
+      </c>
+      <c r="AB18" t="str">
+        <v/>
+      </c>
+      <c r="AC18" t="str">
+        <v>持续无效→检查班主任自身心智化水平（Q03 识别/诊断能力）</v>
+      </c>
+      <c r="AD18" t="str">
+        <v/>
+      </c>
+      <c r="AE18" t="str">
+        <v/>
+      </c>
+      <c r="AF18" t="str">
+        <v/>
+      </c>
+      <c r="AG18" t="str">
+        <v/>
+      </c>
+      <c r="AH18" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SC_RX_18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>心智化危机回应（不撑不退）</v>
+      </c>
+      <c r="C19" t="str">
+        <v>心智化危机回应（</v>
+      </c>
+      <c r="D19" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E19" t="str">
+        <v>script</v>
+      </c>
+      <c r="F19" t="str">
+        <v>all</v>
+      </c>
+      <c r="G19" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H19" t="str">
+        <v>自杀/自伤/严重攻击信号；情绪失控反复；心智化缺失是深层因素</v>
+      </c>
+      <c r="I19" t="str">
+        <v>high</v>
+      </c>
+      <c r="J19" t="str">
+        <v>C2;E2</v>
+      </c>
+      <c r="K19" t="str">
+        <v>情绪调节型;教养不当型</v>
+      </c>
+      <c r="L19" t="str">
+        <v>情绪,家庭,安全,student_case</v>
+      </c>
+      <c r="M19" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v>确保学生处于安全环境并有人陪伴，不让学生独处；不撑不退：保持平静语气和稳定身体姿态，不防御、不争吵、不评判；心智化四步回应：看见情绪→命名情绪→接纳情绪→连接需求；安全流程优先：通知心理总监+年级组长+德育处，与危机评估并行</v>
+      </c>
+      <c r="P19" t="str">
+        <v>我看到你还是很激动。没关系，我们不急。我就在这里陪着你。</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>即时：情绪强度降低；长期：主动求助增加</v>
+      </c>
+      <c r="R19" t="str">
+        <v>即时</v>
+      </c>
+      <c r="S19" t="str">
+        <v>至情绪平复</v>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v>不要在冲突过程中训斥学生（高唤醒状态下训斥无效）；不要让学生独处；不要承诺保密；不用「别想太多」「你要坚强」之类的话</v>
+      </c>
+      <c r="V19" t="str">
+        <v/>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
+        <v/>
+      </c>
+      <c r="Z19" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 E2/C2 危机 / 术语库 V2.0 13 SA01-SA05）</v>
+      </c>
+      <c r="AB19" t="str">
+        <v/>
+      </c>
+      <c r="AC19" t="str">
+        <v>安全流程优先——心智化回应与危机评估并行；出现自伤信号按 SA01 流程执行</v>
+      </c>
+      <c r="AD19" t="str">
+        <v/>
+      </c>
+      <c r="AE19" t="str">
+        <v/>
+      </c>
+      <c r="AF19" t="str">
+        <v/>
+      </c>
+      <c r="AG19" t="str">
+        <v/>
+      </c>
+      <c r="AH19" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SC_RX_19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>优势入口+心智化底色（通用叠加）</v>
+      </c>
+      <c r="C20" t="str">
+        <v>优势入口+心智化</v>
+      </c>
+      <c r="D20" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E20" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F20" t="str">
+        <v>all</v>
+      </c>
+      <c r="G20" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H20" t="str">
+        <v>所有编码均可叠加 T11 优势锚定 + T12 心智化底色</v>
+      </c>
+      <c r="I20" t="str">
+        <v>low</v>
+      </c>
+      <c r="J20" t="str">
+        <v>A1;A2;A3;B1;B2;B3;C1;C2;C3;D1;D2;D3;E1;E2;E3</v>
+      </c>
+      <c r="K20" t="str">
+        <v>注意力分散型;动机缺失型;技能不足型;课堂纪律型;规则习惯型;攻击冲动型;焦虑退缩型;情绪调节型;低自尊型;同伴冲突型;社交退缩型;技能缺失型;亲子紧张型;教养不当型;支持缺位型</v>
+      </c>
+      <c r="L20" t="str">
+        <v>学习,行为,情绪,社交,家庭,安全,student_case</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v>T12 不替代 T1-T11，而是所有技术的「操作系统」</v>
+      </c>
+      <c r="O20" t="str">
+        <v>为命中编码选择主技术（编码匹配主技术 T1-T8）；用 T11 优势锚定优化技术入口：所有技术经由优势通道进入；所有师生互动以 T12 心智化为底层语言；2 周评估干预效率和关系质量</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v>干预效率和关系质量双重提升</v>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v>不用于替代危机处置</v>
+      </c>
+      <c r="V20" t="str">
+        <v/>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
+        <v/>
+      </c>
+      <c r="Z20" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>班主任干预技术处方库 V1.0（① 处方速查表 T9/T10 全编码通用）</v>
+      </c>
+      <c r="AB20" t="str">
+        <v/>
+      </c>
+      <c r="AC20" t="str">
+        <v>T11 失效→优势定位不准；T12 失效→关系地基不稳</v>
+      </c>
+      <c r="AD20" t="str">
+        <v/>
+      </c>
+      <c r="AE20" t="str">
+        <v/>
+      </c>
+      <c r="AF20" t="str">
+        <v/>
+      </c>
+      <c r="AG20" t="str">
+        <v/>
+      </c>
+      <c r="AH20" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SC_RX_20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>定时器分段法</v>
+      </c>
+      <c r="C21" t="str">
+        <v>定时器分段法</v>
+      </c>
+      <c r="D21" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E21" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F21" t="str">
+        <v>all</v>
+      </c>
+      <c r="G21" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H21" t="str">
+        <v>A1 注意力分散：作业拖拉、完不成课堂任务、注意力维持困难</v>
+      </c>
+      <c r="I21" t="str">
+        <v>low</v>
+      </c>
+      <c r="J21" t="str">
+        <v>A1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>注意力分散型</v>
+      </c>
+      <c r="L21" t="str">
+        <v>学习,student_case</v>
+      </c>
+      <c r="M21" t="str">
+        <v>SC_S1D2</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v>Step 0（依恋增强版·关系锚定，约 30 秒）：蹲下平视——「我就在旁边，做完这一段你可以随时来找我核对」；S1 把任务分成 5-10 分钟小段，每段一个明确目标；S2 用可视化定时器倒计时，让孩子看到剩余时间；S3 完成一段休息 2 分钟，完成 3 段获得较大奖励</v>
+      </c>
+      <c r="P21" t="str">
+        <v>我就在旁边，做完这一段你可以随时来找我核对。</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>1 周内作业效率明显改善</v>
+      </c>
+      <c r="R21" t="str">
+        <v>5-10 分钟/段</v>
+      </c>
+      <c r="S21" t="str">
+        <v>每天×2 周</v>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v>奖励首选社会性奖励（自由时间、当小助手），物质奖励辅助；定时器必须可视化；Step 0 不替代 Step 1-3</v>
+      </c>
+      <c r="V21" t="str">
+        <v/>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
+        <v/>
+      </c>
+      <c r="Z21" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>术语库 V2.0（07 干预技术 T1）/ 业务指导手册 V3.0（4.1）</v>
+      </c>
+      <c r="AB21" t="str">
+        <v/>
+      </c>
+      <c r="AC21" t="str">
+        <v>段长缩短至 3 分钟甚至 1 分钟，目标改为「专注完成一段」；仍困难→先确认是否难度超载并降低任务难度</v>
+      </c>
+      <c r="AD21" t="str">
+        <v/>
+      </c>
+      <c r="AE21" t="str">
+        <v/>
+      </c>
+      <c r="AF21" t="str">
+        <v/>
+      </c>
+      <c r="AG21" t="str">
+        <v/>
+      </c>
+      <c r="AH21" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI21" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SC_RX_21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>注意力信号约定</v>
+      </c>
+      <c r="C22" t="str">
+        <v>注意力信号约定</v>
+      </c>
+      <c r="D22" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E22" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F22" t="str">
+        <v>all</v>
+      </c>
+      <c r="G22" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H22" t="str">
+        <v>A1 课堂走神型：上课走神频繁，需反复提醒</v>
+      </c>
+      <c r="I22" t="str">
+        <v>low</v>
+      </c>
+      <c r="J22" t="str">
+        <v>A1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>注意力分散型</v>
+      </c>
+      <c r="L22" t="str">
+        <v>学习,student_case</v>
+      </c>
+      <c r="M22" t="str">
+        <v>SC_S1D2</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v>S1 与孩子私下约定专属暗号（手势/桌面卡片翻转/座位微调，无惩罚性）；S2 每次走神用暗号提醒，不做任何语言批评；S3 连续一周走神明显下降后逐步退出暗号；依恋增强版：约定时说明「这个暗号是我们俩之间的小秘密——它代表「我知道你在努力，我看到了」」，退出时明确告知约定一直在</v>
+      </c>
+      <c r="P22" t="str">
+        <v>这个暗号是我们俩之间的小秘密——它代表「我知道你在努力，我看到了」。</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>1-2 周走神次数显著下降</v>
+      </c>
+      <c r="R22" t="str">
+        <v>即时</v>
+      </c>
+      <c r="S22" t="str">
+        <v>1-2 周</v>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v>暗号的核心是「非惩罚性」——暗号不是「抓到你了」的信号，而是「我注意到你在坚持」的信号</v>
+      </c>
+      <c r="V22" t="str">
+        <v/>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+      <c r="Z22" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>术语库 V2.0（07 干预技术 T2）/ 业务指导手册 V3.0（4.1）</v>
+      </c>
+      <c r="AB22" t="str">
+        <v/>
+      </c>
+      <c r="AC22" t="str">
+        <v>暗号太显眼→换更隐蔽方式；走神原因是课程难度远超水平→先降任务难度</v>
+      </c>
+      <c r="AD22" t="str">
+        <v/>
+      </c>
+      <c r="AE22" t="str">
+        <v/>
+      </c>
+      <c r="AF22" t="str">
+        <v/>
+      </c>
+      <c r="AG22" t="str">
+        <v/>
+      </c>
+      <c r="AH22" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI22" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SC_RX_22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>渐进参与计划</v>
+      </c>
+      <c r="C23" t="str">
+        <v>渐进参与计划</v>
+      </c>
+      <c r="D23" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E23" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F23" t="str">
+        <v>all</v>
+      </c>
+      <c r="G23" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H23" t="str">
+        <v>A1/C1 不敢举手、课堂退缩的学生</v>
+      </c>
+      <c r="I23" t="str">
+        <v>low</v>
+      </c>
+      <c r="J23" t="str">
+        <v>A1;C1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>注意力分散型;焦虑退缩型</v>
+      </c>
+      <c r="L23" t="str">
+        <v>学习,情绪,student_case</v>
+      </c>
+      <c r="M23" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v>Step 0（依恋增强版·安全基地启动）：与学生进行 1-2 分钟一对一非学习闲聊；第 1 周：老师看向你时保持目光接触；第 2 周：知道答案时在心里说一遍；第 3 周：对同桌小声说出答案；第 4 周：举手一次（事先与老师约定，老师会叫你），每完成一阶段给具体口头表扬</v>
+      </c>
+      <c r="P23" t="str">
+        <v>放轻松，我们只是练习，不是考试。</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>4 周内实现首次举手</v>
+      </c>
+      <c r="R23" t="str">
+        <v>即时</v>
+      </c>
+      <c r="S23" t="str">
+        <v>4 周渐进</v>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v>前两周重点不是「行为达标」而是「建立安全感」；焦虑状态下的社交尝试成功率远低于安全状态</v>
+      </c>
+      <c r="V23" t="str">
+        <v/>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+      <c r="Z23" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA23" t="str">
+        <v>术语库 V2.0（07 干预技术 T3）/ 业务指导手册 V3.0（4.1）</v>
+      </c>
+      <c r="AB23" t="str">
+        <v/>
+      </c>
+      <c r="AC23" t="str">
+        <v>某阶段停滞超过 2 周→退回上一阶段重建信心；仍困难→检查是否存在被同伴嘲笑等环境因素</v>
+      </c>
+      <c r="AD23" t="str">
+        <v/>
+      </c>
+      <c r="AE23" t="str">
+        <v/>
+      </c>
+      <c r="AF23" t="str">
+        <v/>
+      </c>
+      <c r="AG23" t="str">
+        <v/>
+      </c>
+      <c r="AH23" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI23" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SC_RX_23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>三步行为契约</v>
+      </c>
+      <c r="C24" t="str">
+        <v>三步行为契约</v>
+      </c>
+      <c r="D24" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E24" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F24" t="str">
+        <v>all</v>
+      </c>
+      <c r="G24" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H24" t="str">
+        <v>B1/B2/B3 课堂纪律、规则习惯、攻击冲动类行为问题</v>
+      </c>
+      <c r="I24" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J24" t="str">
+        <v>B1;B2;B3</v>
+      </c>
+      <c r="K24" t="str">
+        <v>课堂纪律型;规则习惯型;攻击冲动型</v>
+      </c>
+      <c r="L24" t="str">
+        <v>行为,student_case</v>
+      </c>
+      <c r="M24" t="str">
+        <v>SC_S1D3</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v>第一步·共定目标：具体可测（不是「认真听讲」而是「老师叫我名字时我能站起来」）；第二步·明确奖励：首选社会性奖励（额外自由时间/当小助手/优先选择权），物质奖励辅助；第三步·每日复盘：放学最后 2 分钟 30 秒复盘——做到了吗？为什么？明天怎么调整？；依恋增强版：增加关系目标——「这一周当你沮丧或想发火时，可以来找我，我们一起想办法」</v>
+      </c>
+      <c r="P24" t="str">
+        <v>你愿意来找我，这本身就是最大的进步。你做到了我们约好的事，这让我觉得我们的约定是有力量的。</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>1 周目标达标率&gt;60%；2 周&gt;80%</v>
+      </c>
+      <c r="R24" t="str">
+        <v>5 分钟</v>
+      </c>
+      <c r="S24" t="str">
+        <v>2 周一个周期</v>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v>低年段：老师主导+画图辅助+当日兑现；中年段：师生协商+周奖励；高年段：学生主导起草+同伴见证；不以惩罚为手段</v>
+      </c>
+      <c r="V24" t="str">
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+      <c r="Z24" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>术语库 V2.0（07 干预技术 T4）/ 业务指导手册 V3.0（4.2）</v>
+      </c>
+      <c r="AB24" t="str">
+        <v/>
+      </c>
+      <c r="AC24" t="str">
+        <v>目标再分小一半（一节课→前 15 分钟）；问孩子「你觉得什么奖励有意思」；用 ABC 分析回溯触发和后果</v>
+      </c>
+      <c r="AD24" t="str">
+        <v/>
+      </c>
+      <c r="AE24" t="str">
+        <v/>
+      </c>
+      <c r="AF24" t="str">
+        <v/>
+      </c>
+      <c r="AG24" t="str">
+        <v/>
+      </c>
+      <c r="AH24" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI24" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SC_RX_24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>关系修复目标</v>
+      </c>
+      <c r="C25" t="str">
+        <v>关系修复目标</v>
+      </c>
+      <c r="D25" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E25" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F25" t="str">
+        <v>all</v>
+      </c>
+      <c r="G25" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H25" t="str">
+        <v>所有行为契约场景中，行为目标反复失败或存在不安全依恋信号时</v>
+      </c>
+      <c r="I25" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J25" t="str">
+        <v>B1;B2;B3</v>
+      </c>
+      <c r="K25" t="str">
+        <v>课堂纪律型;规则习惯型;攻击冲动型</v>
+      </c>
+      <c r="L25" t="str">
+        <v>行为,student_case</v>
+      </c>
+      <c r="M25" t="str">
+        <v>SC_S1D3</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v>在 S4 方案中增设 S4-relation 目标（不单独作为结案标准，与行为目标并列记录）；关系修复≠「让学生喜欢我」＝「让学生感受到这个关系是安全的、可预测的」；以周为周期评估：学生主动发起互动的次数是否上升；行为目标反复失败→先检查关系目标进展（不是技术问题而是关系问题）</v>
+      </c>
+      <c r="P25" t="str">
+        <v>无论你做什么，我都不会变成伤害你的人——这是我的承诺，不是你的测试。</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>过程性指标：学生感受到关系安全、可预测，进展比行为更根本</v>
+      </c>
+      <c r="R25" t="str">
+        <v>持续</v>
+      </c>
+      <c r="S25" t="str">
+        <v>以月为单位积累</v>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v>不因行为挑战而放弃关系连接——混乱型最需要「不被抛弃」的体验</v>
+      </c>
+      <c r="V25" t="str">
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+      <c r="Z25" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>术语库 V2.0（07 干预技术 T4+）</v>
+      </c>
+      <c r="AB25" t="str">
+        <v/>
+      </c>
+      <c r="AC25" t="str">
+        <v>行为目标反复失败→先检查关系目标进展；关系地基不稳时上层建筑必摇晃</v>
+      </c>
+      <c r="AD25" t="str">
+        <v/>
+      </c>
+      <c r="AE25" t="str">
+        <v/>
+      </c>
+      <c r="AF25" t="str">
+        <v/>
+      </c>
+      <c r="AG25" t="str">
+        <v/>
+      </c>
+      <c r="AH25" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI25" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SC_RX_25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>情绪命名与接纳</v>
+      </c>
+      <c r="C26" t="str">
+        <v>情绪命名与接纳</v>
+      </c>
+      <c r="D26" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E26" t="str">
+        <v>script</v>
+      </c>
+      <c r="F26" t="str">
+        <v>all</v>
+      </c>
+      <c r="G26" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H26" t="str">
+        <v>C1/C2/C3 所有情绪场景：强烈情绪、情绪崩溃、自我否定</v>
+      </c>
+      <c r="I26" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J26" t="str">
+        <v>C1;C2;C3</v>
+      </c>
+      <c r="K26" t="str">
+        <v>焦虑退缩型;情绪调节型;低自尊型</v>
+      </c>
+      <c r="L26" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="M26" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v>S1 命名情绪（不先解决问题）：低年级——「我看到你拳头攥得很紧，是叫「生气」吗？」；高年级——「用一个词形容你现在的心情」；S2 接纳情绪：「谢谢你告诉我。生气或难过是正常的，每个人都会有。」；S3 才进入问题解决；依恋增强版：增加无条件接纳表述——「无论你是因为什么有这种感觉，你都可以告诉我。我在这里陪着你」</v>
+      </c>
+      <c r="P26" t="str">
+        <v>无论你是因为什么有这种感觉，你都可以告诉我。有情绪是正常的，我在这里陪着你。</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>即时降低情绪强度，缩短平复时间（激活前额叶，抑制杏仁核警报）</v>
+      </c>
+      <c r="R26" t="str">
+        <v>3-5 分钟</v>
+      </c>
+      <c r="S26" t="str">
+        <v>即时</v>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v>接纳的是情绪，规范的是行为——「你可以生气，但不可以打人」；不因行为好坏而条件性连接（Carl Rogers 无条件积极关注的操作化）</v>
+      </c>
+      <c r="V26" t="str">
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+      <c r="Z26" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA26" t="str">
+        <v>术语库 V2.0（07 干预技术 T7）/ 业务指导手册 V3.0（4.3）</v>
+      </c>
+      <c r="AB26" t="str">
+        <v/>
+      </c>
+      <c r="AC26" t="str">
+        <v>说不出→提供选项（&lt;3 个）；拒绝沟通→不说教不强求，安静陪伴后：「我就在这，你准备好了随时可以找我」</v>
+      </c>
+      <c r="AD26" t="str">
+        <v/>
+      </c>
+      <c r="AE26" t="str">
+        <v/>
+      </c>
+      <c r="AF26" t="str">
+        <v/>
+      </c>
+      <c r="AG26" t="str">
+        <v/>
+      </c>
+      <c r="AH26" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI26" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SC_RX_26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>优势发现日记</v>
+      </c>
+      <c r="C27" t="str">
+        <v>优势发现日记</v>
+      </c>
+      <c r="D27" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E27" t="str">
+        <v>worksheet</v>
+      </c>
+      <c r="F27" t="str">
+        <v>all</v>
+      </c>
+      <c r="G27" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H27" t="str">
+        <v>C3 低自尊：常说「我不行」「我笨」，自我否定明显</v>
+      </c>
+      <c r="I27" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J27" t="str">
+        <v>C3</v>
+      </c>
+      <c r="K27" t="str">
+        <v>低自尊型</v>
+      </c>
+      <c r="L27" t="str">
+        <v>情绪,student_case</v>
+      </c>
+      <c r="M27" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v>启动前调取该生优势测评 Top2-3 类型，优点选择优先从优势领域切入；Step 0（依恋增强版·关系预热）：「我想和你一起发现你的优点——不是因为你做错了什么，而是因为我想更多地了解你好的那一面」；S1 每天找 1-2 件「今天我做得不错的事」，具体到行为；S2 累计一周后在班会上以「本周 XX 之星」等形式公开肯定；S3 连续 4 周后让孩子自己写，老师逐步退出</v>
+      </c>
+      <c r="P27" t="str">
+        <v>我想和你一起发现你的优点——不是因为你做错了什么要改正，而是因为我想更多地了解你好的那一面。</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>4 周后自我否定语言明显减少</v>
+      </c>
+      <c r="R27" t="str">
+        <v>5 分钟</v>
+      </c>
+      <c r="S27" t="str">
+        <v>4 周</v>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v>「具体到粒度的看见」对不安全依恋儿童的意义远大于模糊的「你很棒」；优先从优势领域切入</v>
+      </c>
+      <c r="V27" t="str">
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+      <c r="Z27" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA27" t="str">
+        <v>术语库 V2.0（07 干预技术 T8）/ 业务指导手册 V3.0（4.3）</v>
+      </c>
+      <c r="AB27" t="str">
+        <v/>
+      </c>
+      <c r="AC27" t="str">
+        <v>找不出优点→老师说「今天你做的最小一件好事」；所有科目都失败→从非学业优势领域找起点（值日/助人/运动会/画画）</v>
+      </c>
+      <c r="AD27" t="str">
+        <v/>
+      </c>
+      <c r="AE27" t="str">
+        <v/>
+      </c>
+      <c r="AF27" t="str">
+        <v/>
+      </c>
+      <c r="AG27" t="str">
+        <v/>
+      </c>
+      <c r="AH27" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI27" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SC_RX_27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>社交剧本练习</v>
+      </c>
+      <c r="C28" t="str">
+        <v>社交剧本练习</v>
+      </c>
+      <c r="D28" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E28" t="str">
+        <v>exercise</v>
+      </c>
+      <c r="F28" t="str">
+        <v>all</v>
+      </c>
+      <c r="G28" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H28" t="str">
+        <v>D3 社交技能缺失：不会加入游戏、读不懂社交线索</v>
+      </c>
+      <c r="I28" t="str">
+        <v>low</v>
+      </c>
+      <c r="J28" t="str">
+        <v>D3</v>
+      </c>
+      <c r="K28" t="str">
+        <v>技能缺失型</v>
+      </c>
+      <c r="L28" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="M28" t="str">
+        <v>SC_S1D5</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v>Step 0（依恋增强版·安全基地预热）：1-2 分钟轻松对话，让学生感受「此刻我是安全的，这个人不会评判我」；S1 设计简短社交剧本——「走近正在玩的小组，站旁边看 30 秒，等一个自然停顿，说「看起来好好玩，我可以加入吗？」」；S2 老师先做示范表演，再让孩子练习 3 遍；S3 在真实场景中观察使用情况，当天给反馈</v>
+      </c>
+      <c r="P28" t="str">
+        <v>放轻松，我们只是练习，不是考试。</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>2 周内开始尝试在真实场景中使用剧本行为</v>
+      </c>
+      <c r="R28" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S28" t="str">
+        <v>2 周</v>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v>安全基地预热不是浪费时间，是 T9 效果的最强预测因素之一</v>
+      </c>
+      <c r="V28" t="str">
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
+        <v/>
+      </c>
+      <c r="Z28" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA28" t="str">
+        <v>术语库 V2.0（07 干预技术 T9）/ 业务指导手册 V3.0（4.4）</v>
+      </c>
+      <c r="AB28" t="str">
+        <v/>
+      </c>
+      <c r="AC28" t="str">
+        <v>记不住台词→缩减为一个核心句；真实场景不敢用→先在小范围内练习（同桌）</v>
+      </c>
+      <c r="AD28" t="str">
+        <v/>
+      </c>
+      <c r="AE28" t="str">
+        <v/>
+      </c>
+      <c r="AF28" t="str">
+        <v/>
+      </c>
+      <c r="AG28" t="str">
+        <v/>
+      </c>
+      <c r="AH28" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI28" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SC_RX_28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>友谊桥同伴配对</v>
+      </c>
+      <c r="C29" t="str">
+        <v>友谊桥同伴配对</v>
+      </c>
+      <c r="D29" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E29" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F29" t="str">
+        <v>all</v>
+      </c>
+      <c r="G29" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H29" t="str">
+        <v>D2 社交退缩：自由活动时间独自一人，不主动接近同伴</v>
+      </c>
+      <c r="I29" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J29" t="str">
+        <v>D2</v>
+      </c>
+      <c r="K29" t="str">
+        <v>社交退缩型</v>
+      </c>
+      <c r="L29" t="str">
+        <v>社交,student_case</v>
+      </c>
+      <c r="M29" t="str">
+        <v>SC_S1D5</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v>S1 安排性格温和、社交能力中等的同伴坐在旁边（不选最强的——碾压式配对适得其反）；S2 设计需要两人协作才能完成的任务；S3 从「任务导向的互动」自然过渡到「社交导向的互动」；S4 每周末分别问双方感受；依恋增强版：配对前单独沟通同伴——「XX 同学需要一个朋友，我想请你帮忙……这不是任务，是邀请」</v>
+      </c>
+      <c r="P29" t="str">
+        <v>XX 同学需要一个朋友，我想请你帮忙，因为你是我见过最温和、最让人放心的同学。这不是任务，是邀请——你愿意试试看吗？</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>4 周内自由活动时间出现固定玩伴</v>
+      </c>
+      <c r="R29" t="str">
+        <v>持续</v>
+      </c>
+      <c r="S29" t="str">
+        <v>4 周</v>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v>不选最强的同伴；不要忽视同伴的心理状态（温和型同伴本质在扮演「微型安全基地」，过度给予无回馈会导致同伴耗竭）</v>
+      </c>
+      <c r="V29" t="str">
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <v/>
+      </c>
+      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
+        <v/>
+      </c>
+      <c r="Z29" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA29" t="str">
+        <v>术语库 V2.0（07 干预技术 T10）/ 业务指导手册 V3.0（4.4）</v>
+      </c>
+      <c r="AB29" t="str">
+        <v/>
+      </c>
+      <c r="AC29" t="str">
+        <v>同伴不匹配→换人，关键是互补而不碾压；两人都退缩→改为三人小组降低一对一社交压力</v>
+      </c>
+      <c r="AD29" t="str">
+        <v/>
+      </c>
+      <c r="AE29" t="str">
+        <v/>
+      </c>
+      <c r="AF29" t="str">
+        <v/>
+      </c>
+      <c r="AG29" t="str">
+        <v/>
+      </c>
+      <c r="AH29" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI29" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SC_RX_29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>优势锚定法</v>
+      </c>
+      <c r="C30" t="str">
+        <v>优势锚定法</v>
+      </c>
+      <c r="D30" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E30" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F30" t="str">
+        <v>all</v>
+      </c>
+      <c r="G30" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H30" t="str">
+        <v>所有编码类型；可作为主技术独立使用（S0 路径），也可作为 T1-T10 的锚点技术搭配使用</v>
+      </c>
+      <c r="I30" t="str">
+        <v>low</v>
+      </c>
+      <c r="J30" t="str">
+        <v>A1;A2;A3;B1;B2;B3;C1;C2;C3;D1;D2;D3;E1;E2;E3</v>
+      </c>
+      <c r="K30" t="str">
+        <v>注意力分散型;动机缺失型;技能不足型;课堂纪律型;规则习惯型;攻击冲动型;焦虑退缩型;情绪调节型;低自尊型;同伴冲突型;社交退缩型;技能缺失型;亲子紧张型;教养不当型;支持缺位型</v>
+      </c>
+      <c r="L30" t="str">
+        <v>学习,行为,情绪,社交,家庭,安全,student_case</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v>S1 优势定位：从优势测评获取 Top2-3 优势类型（1-2 年级 50 题版/3-6 年级 20 题版），未测评→安排测评或教师观察法；S2 优势-问题匹配：优势类型与问题编码交叉分析，「用优势通道解决弱势问题」；S3 优势嵌入式方案：格式「主技术 T1+优势适配：因该生身体动觉型，将休息奖励改为 1 分钟运动」；S4 验证优势假设：执行 2 周后评估，无效→检查优势定位准确性与匹配合理性，必要时回到 S1</v>
+      </c>
+      <c r="P30" t="str">
+        <v>用优势通道解决弱势问题——同样的技术经由不同优势通道进入，效果差异巨大。</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>同等干预技术经由优势通道进入，效果提升显著；2 周可验证优势假设</v>
+      </c>
+      <c r="R30" t="str">
+        <v>15 分钟</v>
+      </c>
+      <c r="S30" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v>优势锚定法不是替代 T1-T8，而是为它们提供「入口优化」</v>
+      </c>
+      <c r="V30" t="str">
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <v/>
+      </c>
+      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
+        <v/>
+      </c>
+      <c r="Z30" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA30" t="str">
+        <v>术语库 V2.0（07 干预技术 T11）/ 业务指导手册 V3.0（4.5）</v>
+      </c>
+      <c r="AB30" t="str">
+        <v/>
+      </c>
+      <c r="AC30" t="str">
+        <v>优势定位不准→重测或观察；优势-问题匹配不合理→回 S1 重定位</v>
+      </c>
+      <c r="AD30" t="str">
+        <v/>
+      </c>
+      <c r="AE30" t="str">
+        <v/>
+      </c>
+      <c r="AF30" t="str">
+        <v/>
+      </c>
+      <c r="AG30" t="str">
+        <v/>
+      </c>
+      <c r="AH30" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI30" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SC_RX_30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>优势验证环节</v>
+      </c>
+      <c r="C31" t="str">
+        <v>优势验证环节</v>
+      </c>
+      <c r="D31" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E31" t="str">
+        <v>framework</v>
+      </c>
+      <c r="F31" t="str">
+        <v>all</v>
+      </c>
+      <c r="G31" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H31" t="str">
+        <v>不安全依恋学生：优势定位后需要绕过认知防御建立自我确认</v>
+      </c>
+      <c r="I31" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J31" t="str">
+        <v>C2;C3;E1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>情绪调节型;低自尊型;亲子紧张型</v>
+      </c>
+      <c r="L31" t="str">
+        <v>情绪,家庭,student_case</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v>在优势定位后增加优势验证——不告诉学生「你有这个优势」，而是通过具体活动让他「体验」到；例：空间智能→拼装任务让他「做出来」；人类型→帮助小同学完成一件事；任务完成后不急着表扬，问：「你觉得你刚才做了什么让你自己觉得挺厉害？」；引导他自己命名优势体验</v>
+      </c>
+      <c r="P31" t="str">
+        <v>你觉得你刚才做了什么让你自己觉得挺厉害？</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>体验到的能力感比被告知的更深刻——绕过认知防御直接进入行动层面自我确认</v>
+      </c>
+      <c r="R31" t="str">
+        <v>10 分钟</v>
+      </c>
+      <c r="S31" t="str">
+        <v>每次优势活动后</v>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <v>任务完成后不说「你真棒」——不安全依恋学生倾向于质疑语言肯定（「老师只是在安慰我」），但体验无法被否认</v>
+      </c>
+      <c r="V31" t="str">
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <v/>
+      </c>
+      <c r="X31" t="str">
+        <v/>
+      </c>
+      <c r="Y31" t="str">
+        <v/>
+      </c>
+      <c r="Z31" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA31" t="str">
+        <v>术语库 V2.0（07 干预技术 T11+ / 10 优势测评体系 AD08）</v>
+      </c>
+      <c r="AB31" t="str">
+        <v/>
+      </c>
+      <c r="AC31" t="str">
+        <v>学生拒绝参与→先从低压力活动开始，不强迫</v>
+      </c>
+      <c r="AD31" t="str">
+        <v/>
+      </c>
+      <c r="AE31" t="str">
+        <v/>
+      </c>
+      <c r="AF31" t="str">
+        <v/>
+      </c>
+      <c r="AG31" t="str">
+        <v/>
+      </c>
+      <c r="AH31" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI31" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>心智化回应技术</v>
+      </c>
+      <c r="C32" t="str">
+        <v>心智化回应技术</v>
+      </c>
+      <c r="D32" t="str">
+        <v>student_case</v>
+      </c>
+      <c r="E32" t="str">
+        <v>script</v>
+      </c>
+      <c r="F32" t="str">
+        <v>all</v>
+      </c>
+      <c r="G32" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="H32" t="str">
+        <v>C1/C2/C3/D2/E1 优先；所有师生互动底层语言</v>
+      </c>
+      <c r="I32" t="str">
+        <v>medium</v>
+      </c>
+      <c r="J32" t="str">
+        <v>C1;C2;C3;D2;E1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>焦虑退缩型;情绪调节型;低自尊型;社交退缩型;亲子紧张型</v>
+      </c>
+      <c r="L32" t="str">
+        <v>情绪,社交,家庭,student_case</v>
+      </c>
+      <c r="M32" t="str">
+        <v>SC_S1D4</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v>S1 看见情绪（识别）：「我看到你攥紧拳头/眼睛红了/声音在发抖……」；S2 命名情绪（表达）：「你现在的感觉，是不是叫「生气」/「委屈」/「害怕」？」（低年级可用 6 张基础情绪卡片）；S3 接纳情绪（调控）：「有这样的感觉是正常的。谢谢你告诉我。」（接纳的是情绪，规范的是行为）；S4 连接需求（心智化升级）：「你觉得刚才那么生气，是因为想要什么？」；班级层面：每天 1 次情绪天气（30 秒）；冲突调解三步心智化；教师自我心智化复盘</v>
+      </c>
+      <c r="P32" t="str">
+        <v>我看到你攥紧了拳头/眼睛红了……你现在的感觉，是不是叫「生气」/「委屈」/「害怕」？有这样的感觉是正常的。谢谢你告诉我。</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>即时：情绪强度降低；短期（2-4 周）：用语言表达情绪；长期（1 学期）：主动求助增加、师生信任增强</v>
+      </c>
+      <c r="R32" t="str">
+        <v>3-10 分钟</v>
+      </c>
+      <c r="S32" t="str">
+        <v>持续</v>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+      <c r="U32" t="str">
+        <v>不评判、不否定、不急于解决问题；接纳的是情绪，规范的是行为——「你可以生气，但不可以打人」</v>
+      </c>
+      <c r="V32" t="str">
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <v/>
+      </c>
+      <c r="X32" t="str">
+        <v/>
+      </c>
+      <c r="Y32" t="str">
+        <v/>
+      </c>
+      <c r="Z32" t="str">
+        <v>A</v>
+      </c>
+      <c r="AA32" t="str">
+        <v>术语库 V2.0（07 干预技术 T12）/ 业务指导手册 V3.0（4.6）</v>
+      </c>
+      <c r="AB32" t="str">
+        <v/>
+      </c>
+      <c r="AC32" t="str">
+        <v>拒绝沟通→不强求：「我就在这」；说不出情绪→给 2-3 选项；情绪升级→不撑不退保持稳定；持续 12 周无改善→转介心理教师</v>
+      </c>
+      <c r="AD32" t="str">
+        <v/>
+      </c>
+      <c r="AE32" t="str">
+        <v/>
+      </c>
+      <c r="AF32" t="str">
+        <v/>
+      </c>
+      <c r="AG32" t="str">
+        <v/>
+      </c>
+      <c r="AH32" t="str">
+        <v>学生个体问题 2.0 文档集（5D6D 一表双轨/处方库 V1.0/术语库 V2.0/手册 V6.0/业务指导手册 V3.0）</v>
+      </c>
+      <c r="AI32" t="str">
+        <v>4.5.0</v>
+      </c>
+      <c r="AJ32" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ32"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J133"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1222,10 +3972,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>连续一周，每次行为发生时记录三栏：A 发生前情境</v>
+        <v>立即启动学校安全流程，暂停学业干预，优先安全</v>
       </c>
       <c r="D2" t="str">
-        <v>连续一周，每次行为发生时记录三栏：A 发生前情境 / B 可观察行为 / C 行为后结果</v>
+        <v>立即启动学校安全流程，暂停学业干预，优先安全</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -1234,13 +3984,13 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>我注意到你最近有些变化，我想先了解你的感受。你可以只说一点点。</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -1254,10 +4004,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>只记录看到的，不写推测和评价</v>
+        <v>通知年级组长与德育处，24 小时内完成安全评估与</v>
       </c>
       <c r="D3" t="str">
-        <v>只记录看到的，不写推测和评价</v>
+        <v>通知年级组长与德育处，24 小时内完成安全评估与安全计划</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -1272,7 +4022,7 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -1286,10 +4036,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一周后统计最高频的 A 和 C</v>
+        <v>通过学校正式渠道启动未成年人保护流程，记录具体信</v>
       </c>
       <c r="D4" t="str">
-        <v>一周后统计最高频的 A 和 C</v>
+        <v>通过学校正式渠道启动未成年人保护流程，记录具体信号（只记录不推测）</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -1304,7 +4054,7 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1318,10 +4068,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>针对最高频的 A 做一次环境调整并观察变化</v>
+        <v>联系心理总监进行安全评估，家校安全沟通</v>
       </c>
       <c r="D5" t="str">
-        <v>针对最高频的 A 做一次环境调整并观察变化</v>
+        <v>联系心理总监进行安全评估，家校安全沟通</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -1336,7 +4086,7 @@
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1350,10 +4100,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="str">
-        <v>选一个不被打扰、非正式的场合</v>
+        <v>开场陈述观察到的事实而非结论（不做诊断不贴标签）</v>
       </c>
       <c r="D6" t="str">
-        <v>选一个不被打扰、非正式的场合</v>
+        <v>开场陈述观察到的事实而非结论（不做诊断不贴标签）</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -1362,13 +4112,13 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>我注意到你这两天午休都一个人待着。你可以只说一点点，不需要马上解释清楚。</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1382,10 +4132,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>从一个具体的观察事实开始，不问「你怎么了」</v>
+        <v>呈现 2-3 个可选方案供家长选择（给选项，不给</v>
       </c>
       <c r="D7" t="str">
-        <v>从一个具体的观察事实开始，不问「你怎么了」</v>
+        <v>呈现 2-3 个可选方案供家长选择（给选项，不给任务）</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -1400,7 +4150,7 @@
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -1414,10 +4164,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="str">
-        <v>给出选择而非追问：「你可以只说一点点，也可以先不</v>
+        <v>强调「我们一起」，让家长有掌控感和参与感</v>
       </c>
       <c r="D8" t="str">
-        <v>给出选择而非追问：「你可以只说一点点，也可以先不说」</v>
+        <v>强调「我们一起」，让家长有掌控感和参与感</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -1432,7 +4182,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -1446,10 +4196,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>结束时明确下一次可以找你的时间和方式</v>
+        <v>用心智化话术·家长版沟通，从「纠错模式」切换到「</v>
       </c>
       <c r="D9" t="str">
-        <v>结束时明确下一次可以找你的时间和方式</v>
+        <v>用心智化话术·家长版沟通，从「纠错模式」切换到「连接模式」</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -1464,7 +4214,7 @@
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -1478,10 +4228,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="str">
-        <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
+        <v>共定目标：具体可测（如「老师叫我名字时我能站起来</v>
       </c>
       <c r="D10" t="str">
-        <v>找一个该学生擅长的领域，设计一个需要合作的小任务</v>
+        <v>共定目标：具体可测（如「老师叫我名字时我能站起来」而非「认真听讲」）</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -1490,13 +4240,13 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>这件事你最在行，你带着他们两个一起弄，周五给大家看看。</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -1510,10 +4260,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>为其匹配一到两位关系中性的同学</v>
+        <v>明确奖励：首选社会性奖励（自由时间/当小助手/优</v>
       </c>
       <c r="D11" t="str">
-        <v>为其匹配一到两位关系中性的同学</v>
+        <v>明确奖励：首选社会性奖励（自由时间/当小助手/优先选择权），物质奖励辅助</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -1528,7 +4278,7 @@
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -1542,10 +4292,10 @@
         <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>任务完成后公开肯定该学生的具体贡献</v>
+        <v>每日复盘：放学 30 秒复盘——做到了吗？为什么</v>
       </c>
       <c r="D12" t="str">
-        <v>任务完成后公开肯定该学生的具体贡献</v>
+        <v>每日复盘：放学 30 秒复盘——做到了吗？为什么？明天怎么调整？</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -1560,7 +4310,7 @@
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -1574,10 +4324,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="str">
-        <v>两周后观察自然互动是否增加</v>
+        <v>依恋增强版：增加关系目标——「当你沮丧或想发火时</v>
       </c>
       <c r="D13" t="str">
-        <v>两周后观察自然互动是否增加</v>
+        <v>依恋增强版：增加关系目标——「当你沮丧或想发火时，可以来找我，我们一起想办法」</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -1592,7 +4342,7 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1606,10 +4356,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="str">
-        <v>整理问题的起止时间线和关键事件</v>
+        <v>关系锚定（约 30 秒）：蹲下平视——「我就在旁</v>
       </c>
       <c r="D14" t="str">
-        <v>整理问题的起止时间线和关键事件</v>
+        <v>关系锚定（约 30 秒）：蹲下平视——「我就在旁边，做完这一段你可以随时来找我核对」</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -1618,13 +4368,13 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>目前我们先基于观察事实协同支持，不做标签判断，重点是看哪些支持对学生有效。</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1638,10 +4388,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>列出已尝试的支持措施和各自效果</v>
+        <v>把任务分成 5-10 分钟小段，每段一个明确目标</v>
       </c>
       <c r="D15" t="str">
-        <v>列出已尝试的支持措施和各自效果</v>
+        <v>把任务分成 5-10 分钟小段，每段一个明确目标</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -1656,7 +4406,7 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1670,10 +4420,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="str">
-        <v>对照三级标准判断当前层级</v>
+        <v>用可视化定时器倒计时，完成一段休息 2 分钟，3</v>
       </c>
       <c r="D16" t="str">
-        <v>对照三级标准判断当前层级</v>
+        <v>用可视化定时器倒计时，完成一段休息 2 分钟，3 段=较大奖励</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1688,7 +4438,7 @@
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1702,10 +4452,10 @@
         <v>4</v>
       </c>
       <c r="C17" t="str">
-        <v>按层级准备对应材料并启动流程</v>
+        <v>叠加 T2 注意力信号约定：私下约定暗号，走神时</v>
       </c>
       <c r="D17" t="str">
-        <v>按层级准备对应材料并启动流程</v>
+        <v>叠加 T2 注意力信号约定：私下约定暗号，走神时用暗号提醒不做语言批评</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1720,7 +4470,7 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1734,10 +4484,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="str">
-        <v>确认学业下降已持续四周以上</v>
+        <v>优势定位：调取优势测评 Top2-3 类型（未测</v>
       </c>
       <c r="D18" t="str">
-        <v>确认学业下降已持续四周以上</v>
+        <v>优势定位：调取优势测评 Top2-3 类型（未测评→安排测评或教师观察法）</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1746,13 +4496,13 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>我们关注的不只是分数，而是他在学习过程中遇到了什么困难。</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1766,10 +4516,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>记录哪些科目、哪些环节受影响最明显</v>
+        <v>优势-问题匹配：用优势通道激活学习动机（如身体动</v>
       </c>
       <c r="D19" t="str">
-        <v>记录哪些科目、哪些环节受影响最明显</v>
+        <v>优势-问题匹配：用优势通道激活学习动机（如身体动觉型→运动间歇奖励）</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1784,7 +4534,7 @@
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1798,10 +4548,10 @@
         <v>3</v>
       </c>
       <c r="C20" t="str">
-        <v>在学习问题模块完成三层诊断</v>
+        <v>叠加 T4 三步行为契约（动机版）：共定目标+社</v>
       </c>
       <c r="D20" t="str">
-        <v>在学习问题模块完成三层诊断</v>
+        <v>叠加 T4 三步行为契约（动机版）：共定目标+社会性奖励+每日复盘</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1816,7 +4566,7 @@
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1830,10 +4580,10 @@
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>按三层诊断结果匹配教学支架</v>
+        <v>2 周评估：优势通道是否奏效，无效则复查定位或调</v>
       </c>
       <c r="D21" t="str">
-        <v>按三层诊断结果匹配教学支架</v>
+        <v>2 周评估：优势通道是否奏效，无效则复查定位或调整匹配路径</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1848,7 +4598,7 @@
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1862,10 +4612,10 @@
         <v>1</v>
       </c>
       <c r="C22" t="str">
-        <v>确保学生当下处于安全环境并有人陪伴</v>
+        <v>确认是否学科基础技能落后（识字量/计算能力/学习</v>
       </c>
       <c r="D22" t="str">
-        <v>确保学生当下处于安全环境并有人陪伴</v>
+        <v>确认是否学科基础技能落后（识字量/计算能力/学习方法）</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1874,13 +4624,13 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>这一步决定后面能不能走下去</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>我现在需要请专业老师一起来看看，我会一直陪着你。</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1894,10 +4644,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>立即联系校内心理专员，说明观察到的具体事实</v>
+        <v>优势锚定学习策略：空间型→思维导图，逻辑型→归纳</v>
       </c>
       <c r="D23" t="str">
-        <v>立即联系校内心理专员，说明观察到的具体事实</v>
+        <v>优势锚定学习策略：空间型→思维导图，逻辑型→归纳分析</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1912,7 +4662,7 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1926,10 +4676,10 @@
         <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>同步通知年级组长和家长</v>
+        <v>降任务难度分级：从当前水平+1 级开始，小步胜利</v>
       </c>
       <c r="D24" t="str">
-        <v>同步通知年级组长和家长</v>
+        <v>降任务难度分级：从当前水平+1 级开始，小步胜利</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1944,7 +4694,7 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -1958,10 +4708,10 @@
         <v>4</v>
       </c>
       <c r="C25" t="str">
-        <v>完整记录时间线，不做任何诊断性表述</v>
+        <v>叠加 T3 渐进参与计划（学业版）逐步建立学习信</v>
       </c>
       <c r="D25" t="str">
-        <v>完整记录时间线，不做任何诊断性表述</v>
+        <v>叠加 T3 渐进参与计划（学业版）逐步建立学习信心</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1976,22 +4726,3478 @@
         <v/>
       </c>
       <c r="I25" t="str">
-        <v>完成本步骤描述的动作</v>
+        <v/>
       </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SC_RX_07</v>
+      </c>
+      <c r="B26" t="str">
+        <v>1</v>
+      </c>
+      <c r="C26" t="str">
+        <v>T4 三步行为契约：共定具体可测目标（如「前 1</v>
+      </c>
+      <c r="D26" t="str">
+        <v>T4 三步行为契约：共定具体可测目标（如「前 15 分钟不讲话」）</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SC_RX_07</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2</v>
+      </c>
+      <c r="C27" t="str">
+        <v>明确社会性奖励，低年段当日兑现、高年段延迟至周末</v>
+      </c>
+      <c r="D27" t="str">
+        <v>明确社会性奖励，低年段当日兑现、高年段延迟至周末</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SC_RX_07</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>每日复盘 30 秒，记录达标情况</v>
+      </c>
+      <c r="D28" t="str">
+        <v>每日复盘 30 秒，记录达标情况</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SC_RX_07</v>
+      </c>
+      <c r="B29" t="str">
+        <v>4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>叠加 T2 注意力信号约定，减少语言批评</v>
+      </c>
+      <c r="D29" t="str">
+        <v>叠加 T2 注意力信号约定，减少语言批评</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SC_RX_08</v>
+      </c>
+      <c r="B30" t="str">
+        <v>1</v>
+      </c>
+      <c r="C30" t="str">
+        <v>T4 三步行为契约：从最易改变的习惯入手（如「一</v>
+      </c>
+      <c r="D30" t="str">
+        <v>T4 三步行为契约：从最易改变的习惯入手（如「一课桌」整理）</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SC_RX_08</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2</v>
+      </c>
+      <c r="C31" t="str">
+        <v>优势锚定量化版：逻辑型→计分系统、图表追踪；动觉</v>
+      </c>
+      <c r="D31" t="str">
+        <v>优势锚定量化版：逻辑型→计分系统、图表追踪；动觉型→动作化规则</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SC_RX_08</v>
+      </c>
+      <c r="B32" t="str">
+        <v>3</v>
+      </c>
+      <c r="C32" t="str">
+        <v>每日复盘+每周奖励</v>
+      </c>
+      <c r="D32" t="str">
+        <v>每日复盘+每周奖励</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SC_RX_08</v>
+      </c>
+      <c r="B33" t="str">
+        <v>4</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2 周评估达标率，持续调整目标粒度</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2 周评估达标率，持续调整目标粒度</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SC_RX_09</v>
+      </c>
+      <c r="B34" t="str">
+        <v>1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>T7 情绪命名与接纳：命名情绪（「我看到你拳头攥</v>
+      </c>
+      <c r="D34" t="str">
+        <v>T7 情绪命名与接纳：命名情绪（「我看到你拳头攥得很紧，是叫「生气」吗？」）</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SC_RX_09</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>无条件接纳：「谢谢你告诉我。生气或难过是正常的，</v>
+      </c>
+      <c r="D35" t="str">
+        <v>无条件接纳：「谢谢你告诉我。生气或难过是正常的，每个人都会有。」</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SC_RX_09</v>
+      </c>
+      <c r="B36" t="str">
+        <v>3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>情绪平复后才进入问题解决</v>
+      </c>
+      <c r="D36" t="str">
+        <v>情绪平复后才进入问题解决</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SC_RX_09</v>
+      </c>
+      <c r="B37" t="str">
+        <v>4</v>
+      </c>
+      <c r="C37" t="str">
+        <v>叠加 T12 心智化回应完整版，情绪升级时「不撑</v>
+      </c>
+      <c r="D37" t="str">
+        <v>叠加 T12 心智化回应完整版，情绪升级时「不撑不退」保持稳定</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SC_RX_10</v>
+      </c>
+      <c r="B38" t="str">
+        <v>1</v>
+      </c>
+      <c r="C38" t="str">
+        <v>T3 渐进参与计划：安全基地启动（1-2 分钟非</v>
+      </c>
+      <c r="D38" t="str">
+        <v>T3 渐进参与计划：安全基地启动（1-2 分钟非学习闲聊）</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SC_RX_10</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>第 1 周：老师看向你时保持目光接触</v>
+      </c>
+      <c r="D39" t="str">
+        <v>第 1 周：老师看向你时保持目光接触</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SC_RX_10</v>
+      </c>
+      <c r="B40" t="str">
+        <v>3</v>
+      </c>
+      <c r="C40" t="str">
+        <v>第 2-3 周：心里说答案→对同桌小声说</v>
+      </c>
+      <c r="D40" t="str">
+        <v>第 2-3 周：心里说答案→对同桌小声说</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SC_RX_10</v>
+      </c>
+      <c r="B41" t="str">
+        <v>4</v>
+      </c>
+      <c r="C41" t="str">
+        <v>第 4 周：举手一次（事先约定，老师会叫你）</v>
+      </c>
+      <c r="D41" t="str">
+        <v>第 4 周：举手一次（事先约定，老师会叫你）</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SC_RX_10</v>
+      </c>
+      <c r="B42" t="str">
+        <v>5</v>
+      </c>
+      <c r="C42" t="str">
+        <v>叠加 T8 优势发现日记积累成功体验</v>
+      </c>
+      <c r="D42" t="str">
+        <v>叠加 T8 优势发现日记积累成功体验</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SC_RX_11</v>
+      </c>
+      <c r="B43" t="str">
+        <v>1</v>
+      </c>
+      <c r="C43" t="str">
+        <v>关系预热：「我想和你一起发现你的优点——不是因为</v>
+      </c>
+      <c r="D43" t="str">
+        <v>关系预热：「我想和你一起发现你的优点——不是因为你做错了什么」</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SC_RX_11</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2</v>
+      </c>
+      <c r="C44" t="str">
+        <v>T8 优势发现日记：每天找 1-2 件「今天做得</v>
+      </c>
+      <c r="D44" t="str">
+        <v>T8 优势发现日记：每天找 1-2 件「今天做得不错的事」，具体到行为、优先优势领域</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SC_RX_11</v>
+      </c>
+      <c r="B45" t="str">
+        <v>3</v>
+      </c>
+      <c r="C45" t="str">
+        <v>累计一周班会上公开肯定（「本周 XX 之星」形式</v>
+      </c>
+      <c r="D45" t="str">
+        <v>累计一周班会上公开肯定（「本周 XX 之星」形式）</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SC_RX_11</v>
+      </c>
+      <c r="B46" t="str">
+        <v>4</v>
+      </c>
+      <c r="C46" t="str">
+        <v>连续 4 周后让学生自己写，老师逐步退出</v>
+      </c>
+      <c r="D46" t="str">
+        <v>连续 4 周后让学生自己写，老师逐步退出</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SC_RX_11</v>
+      </c>
+      <c r="B47" t="str">
+        <v>5</v>
+      </c>
+      <c r="C47" t="str">
+        <v>叠加 T11 优势锚定法持续强化</v>
+      </c>
+      <c r="D47" t="str">
+        <v>叠加 T11 优势锚定法持续强化</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SC_RX_12</v>
+      </c>
+      <c r="B48" t="str">
+        <v>1</v>
+      </c>
+      <c r="C48" t="str">
+        <v>T12 冲突调解三步心智化：先各说一句「我觉得…</v>
+      </c>
+      <c r="D48" t="str">
+        <v>T12 冲突调解三步心智化：先各说一句「我觉得……」</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SC_RX_12</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2</v>
+      </c>
+      <c r="C49" t="str">
+        <v>听完后把对方的话重述一遍（理解他人心理状态）</v>
+      </c>
+      <c r="D49" t="str">
+        <v>听完后把对方的话重述一遍（理解他人心理状态）</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>SC_RX_12</v>
+      </c>
+      <c r="B50" t="str">
+        <v>3</v>
+      </c>
+      <c r="C50" t="str">
+        <v>连接需求：「除了打架，还有什么办法？」</v>
+      </c>
+      <c r="D50" t="str">
+        <v>连接需求：「除了打架，还有什么办法？」</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>SC_RX_12</v>
+      </c>
+      <c r="B51" t="str">
+        <v>4</v>
+      </c>
+      <c r="C51" t="str">
+        <v>叠加 T4 行为契约（社交版）：约定替代行为并正</v>
+      </c>
+      <c r="D51" t="str">
+        <v>叠加 T4 行为契约（社交版）：约定替代行为并正强化</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>SC_RX_13</v>
+      </c>
+      <c r="B52" t="str">
+        <v>1</v>
+      </c>
+      <c r="C52" t="str">
+        <v>T10 友谊桥同伴配对：安排温和、社交能力中等的</v>
+      </c>
+      <c r="D52" t="str">
+        <v>T10 友谊桥同伴配对：安排温和、社交能力中等的同伴（不选最强的）</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>SC_RX_13</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2</v>
+      </c>
+      <c r="C53" t="str">
+        <v>设计需两人协作的任务，从任务互动过渡到社交互动</v>
+      </c>
+      <c r="D53" t="str">
+        <v>设计需两人协作的任务，从任务互动过渡到社交互动</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>SC_RX_13</v>
+      </c>
+      <c r="B54" t="str">
+        <v>3</v>
+      </c>
+      <c r="C54" t="str">
+        <v>每周末分别问双方感受，关注同伴心理状态</v>
+      </c>
+      <c r="D54" t="str">
+        <v>每周末分别问双方感受，关注同伴心理状态</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>SC_RX_13</v>
+      </c>
+      <c r="B55" t="str">
+        <v>4</v>
+      </c>
+      <c r="C55" t="str">
+        <v>叠加 T9 社交剧本练习降低社交启动难度</v>
+      </c>
+      <c r="D55" t="str">
+        <v>叠加 T9 社交剧本练习降低社交启动难度</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>SC_RX_14</v>
+      </c>
+      <c r="B56" t="str">
+        <v>1</v>
+      </c>
+      <c r="C56" t="str">
+        <v>T9 社交剧本练习：安全基地预热（1-2 分钟轻</v>
+      </c>
+      <c r="D56" t="str">
+        <v>T9 社交剧本练习：安全基地预热（1-2 分钟轻松对话）</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>SC_RX_14</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2</v>
+      </c>
+      <c r="C57" t="str">
+        <v>设计简短社交剧本（走近小组站 30 秒→等停顿→</v>
+      </c>
+      <c r="D57" t="str">
+        <v>设计简短社交剧本（走近小组站 30 秒→等停顿→说「我可以加入吗」）</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>SC_RX_14</v>
+      </c>
+      <c r="B58" t="str">
+        <v>3</v>
+      </c>
+      <c r="C58" t="str">
+        <v>老师示范→学生练习 3 遍</v>
+      </c>
+      <c r="D58" t="str">
+        <v>老师示范→学生练习 3 遍</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SC_RX_14</v>
+      </c>
+      <c r="B59" t="str">
+        <v>4</v>
+      </c>
+      <c r="C59" t="str">
+        <v>真实场景观察使用情况，当天反馈</v>
+      </c>
+      <c r="D59" t="str">
+        <v>真实场景观察使用情况，当天反馈</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>SC_RX_14</v>
+      </c>
+      <c r="B60" t="str">
+        <v>5</v>
+      </c>
+      <c r="C60" t="str">
+        <v>叠加 T10 友谊桥提供实践场</v>
+      </c>
+      <c r="D60" t="str">
+        <v>叠加 T10 友谊桥提供实践场</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>SC_RX_15</v>
+      </c>
+      <c r="B61" t="str">
+        <v>1</v>
+      </c>
+      <c r="C61" t="str">
+        <v>T11 优势锚定法（独立·S0 发展）：调取优势</v>
+      </c>
+      <c r="D61" t="str">
+        <v>T11 优势锚定法（独立·S0 发展）：调取优势测评 Top2-3 类型</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>SC_RX_15</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2</v>
+      </c>
+      <c r="C62" t="str">
+        <v>以学校为安全基地：建立稳定可预测的师生关系</v>
+      </c>
+      <c r="D62" t="str">
+        <v>以学校为安全基地：建立稳定可预测的师生关系</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>SC_RX_15</v>
+      </c>
+      <c r="B63" t="str">
+        <v>3</v>
+      </c>
+      <c r="C63" t="str">
+        <v>为优势领域制定 2-3 个学期发展目标，定期跟踪</v>
+      </c>
+      <c r="D63" t="str">
+        <v>为优势领域制定 2-3 个学期发展目标，定期跟踪</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>SC_RX_15</v>
+      </c>
+      <c r="B64" t="str">
+        <v>4</v>
+      </c>
+      <c r="C64" t="str">
+        <v>叠加 T8 优势发现日记积累成功体验</v>
+      </c>
+      <c r="D64" t="str">
+        <v>叠加 T8 优势发现日记积累成功体验</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>SC_RX_15</v>
+      </c>
+      <c r="B65" t="str">
+        <v>5</v>
+      </c>
+      <c r="C65" t="str">
+        <v>定期 Q06 月度追踪</v>
+      </c>
+      <c r="D65" t="str">
+        <v>定期 Q06 月度追踪</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>SC_RX_16</v>
+      </c>
+      <c r="B66" t="str">
+        <v>1</v>
+      </c>
+      <c r="C66" t="str">
+        <v>S0a 识别：确认五维零标记+六维全 A/B+学</v>
+      </c>
+      <c r="D66" t="str">
+        <v>S0a 识别：确认五维零标记+六维全 A/B+学有余力特征（10 分钟）</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>SC_RX_16</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2</v>
+      </c>
+      <c r="C67" t="str">
+        <v>S0b 优势定位：调取优势测评 Top2-3 类</v>
+      </c>
+      <c r="D67" t="str">
+        <v>S0b 优势定位：调取优势测评 Top2-3 类型（1-2 年级 50 题版/3-6 年级 20 题版）</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>SC_RX_16</v>
+      </c>
+      <c r="B68" t="str">
+        <v>3</v>
+      </c>
+      <c r="C68" t="str">
+        <v>S0c 方案制定：T11 独立模式，为每个优势制</v>
+      </c>
+      <c r="D68" t="str">
+        <v>S0c 方案制定：T11 独立模式，为每个优势制定 2-3 个学期发展目标，填入优二代成长规划</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>SC_RX_16</v>
+      </c>
+      <c r="B69" t="str">
+        <v>4</v>
+      </c>
+      <c r="C69" t="str">
+        <v>S0d 月度追踪：每月 Q06 自我探索问卷，关</v>
+      </c>
+      <c r="D69" t="str">
+        <v>S0d 月度追踪：每月 Q06 自我探索问卷，关注自我实现和自我升级维度</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>SC_RX_16</v>
+      </c>
+      <c r="B70" t="str">
+        <v>5</v>
+      </c>
+      <c r="C70" t="str">
+        <v>每学期末复查五维筛查，出现标记→正常转入 S1-</v>
+      </c>
+      <c r="D70" t="str">
+        <v>每学期末复查五维筛查，出现标记→正常转入 S1-S5</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>SC_RX_17</v>
+      </c>
+      <c r="B71" t="str">
+        <v>1</v>
+      </c>
+      <c r="C71" t="str">
+        <v>T12 班级层面心智化：每天 1 次「情绪天气」</v>
+      </c>
+      <c r="D71" t="str">
+        <v>T12 班级层面心智化：每天 1 次「情绪天气」（晴天/多云/小雨/雷雨，30 秒，不点名不追问）</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SC_RX_17</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2</v>
+      </c>
+      <c r="C72" t="str">
+        <v>冲突调解三步心智化（看见情绪→理解他人→连接需求</v>
+      </c>
+      <c r="D72" t="str">
+        <v>冲突调解三步心智化（看见情绪→理解他人→连接需求）</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>SC_RX_17</v>
+      </c>
+      <c r="B73" t="str">
+        <v>3</v>
+      </c>
+      <c r="C73" t="str">
+        <v>教师自我心智化复盘：教师稳定本身就是最强的情绪调</v>
+      </c>
+      <c r="D73" t="str">
+        <v>教师自我心智化复盘：教师稳定本身就是最强的情绪调节信号</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>SC_RX_18</v>
+      </c>
+      <c r="B74" t="str">
+        <v>1</v>
+      </c>
+      <c r="C74" t="str">
+        <v>确保学生处于安全环境并有人陪伴，不让学生独处</v>
+      </c>
+      <c r="D74" t="str">
+        <v>确保学生处于安全环境并有人陪伴，不让学生独处</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>SC_RX_18</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2</v>
+      </c>
+      <c r="C75" t="str">
+        <v>不撑不退：保持平静语气和稳定身体姿态，不防御、不</v>
+      </c>
+      <c r="D75" t="str">
+        <v>不撑不退：保持平静语气和稳定身体姿态，不防御、不争吵、不评判</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>SC_RX_18</v>
+      </c>
+      <c r="B76" t="str">
+        <v>3</v>
+      </c>
+      <c r="C76" t="str">
+        <v>心智化四步回应：看见情绪→命名情绪→接纳情绪→连</v>
+      </c>
+      <c r="D76" t="str">
+        <v>心智化四步回应：看见情绪→命名情绪→接纳情绪→连接需求</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>SC_RX_18</v>
+      </c>
+      <c r="B77" t="str">
+        <v>4</v>
+      </c>
+      <c r="C77" t="str">
+        <v>安全流程优先：通知心理总监+年级组长+德育处，与</v>
+      </c>
+      <c r="D77" t="str">
+        <v>安全流程优先：通知心理总监+年级组长+德育处，与危机评估并行</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SC_RX_19</v>
+      </c>
+      <c r="B78" t="str">
+        <v>1</v>
+      </c>
+      <c r="C78" t="str">
+        <v>为命中编码选择主技术（编码匹配主技术 T1-T8</v>
+      </c>
+      <c r="D78" t="str">
+        <v>为命中编码选择主技术（编码匹配主技术 T1-T8）</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SC_RX_19</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2</v>
+      </c>
+      <c r="C79" t="str">
+        <v>用 T11 优势锚定优化技术入口：所有技术经由优</v>
+      </c>
+      <c r="D79" t="str">
+        <v>用 T11 优势锚定优化技术入口：所有技术经由优势通道进入</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>SC_RX_19</v>
+      </c>
+      <c r="B80" t="str">
+        <v>3</v>
+      </c>
+      <c r="C80" t="str">
+        <v>所有师生互动以 T12 心智化为底层语言</v>
+      </c>
+      <c r="D80" t="str">
+        <v>所有师生互动以 T12 心智化为底层语言</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>SC_RX_19</v>
+      </c>
+      <c r="B81" t="str">
+        <v>4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>2 周评估干预效率和关系质量</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2 周评估干预效率和关系质量</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>SC_RX_20</v>
+      </c>
+      <c r="B82" t="str">
+        <v>1</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Step 0（依恋增强版·关系锚定，约 30 秒</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Step 0（依恋增强版·关系锚定，约 30 秒）：蹲下平视——「我就在旁边，做完这一段你可以随时来找我核对」</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>SC_RX_20</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2</v>
+      </c>
+      <c r="C83" t="str">
+        <v>S1 把任务分成 5-10 分钟小段，每段一个明</v>
+      </c>
+      <c r="D83" t="str">
+        <v>S1 把任务分成 5-10 分钟小段，每段一个明确目标</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>SC_RX_20</v>
+      </c>
+      <c r="B84" t="str">
+        <v>3</v>
+      </c>
+      <c r="C84" t="str">
+        <v>S2 用可视化定时器倒计时，让孩子看到剩余时间</v>
+      </c>
+      <c r="D84" t="str">
+        <v>S2 用可视化定时器倒计时，让孩子看到剩余时间</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>SC_RX_20</v>
+      </c>
+      <c r="B85" t="str">
+        <v>4</v>
+      </c>
+      <c r="C85" t="str">
+        <v>S3 完成一段休息 2 分钟，完成 3 段获得较</v>
+      </c>
+      <c r="D85" t="str">
+        <v>S3 完成一段休息 2 分钟，完成 3 段获得较大奖励</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>SC_RX_21</v>
+      </c>
+      <c r="B86" t="str">
+        <v>1</v>
+      </c>
+      <c r="C86" t="str">
+        <v>S1 与孩子私下约定专属暗号（手势/桌面卡片翻转</v>
+      </c>
+      <c r="D86" t="str">
+        <v>S1 与孩子私下约定专属暗号（手势/桌面卡片翻转/座位微调，无惩罚性）</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>SC_RX_21</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2</v>
+      </c>
+      <c r="C87" t="str">
+        <v>S2 每次走神用暗号提醒，不做任何语言批评</v>
+      </c>
+      <c r="D87" t="str">
+        <v>S2 每次走神用暗号提醒，不做任何语言批评</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>SC_RX_21</v>
+      </c>
+      <c r="B88" t="str">
+        <v>3</v>
+      </c>
+      <c r="C88" t="str">
+        <v>S3 连续一周走神明显下降后逐步退出暗号</v>
+      </c>
+      <c r="D88" t="str">
+        <v>S3 连续一周走神明显下降后逐步退出暗号</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>SC_RX_21</v>
+      </c>
+      <c r="B89" t="str">
+        <v>4</v>
+      </c>
+      <c r="C89" t="str">
+        <v>依恋增强版：约定时说明「这个暗号是我们俩之间的小</v>
+      </c>
+      <c r="D89" t="str">
+        <v>依恋增强版：约定时说明「这个暗号是我们俩之间的小秘密——它代表「我知道你在努力，我看到了」」，退出时明确告知约定一直在</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>SC_RX_22</v>
+      </c>
+      <c r="B90" t="str">
+        <v>1</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Step 0（依恋增强版·安全基地启动）：与学生</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Step 0（依恋增强版·安全基地启动）：与学生进行 1-2 分钟一对一非学习闲聊</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>SC_RX_22</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2</v>
+      </c>
+      <c r="C91" t="str">
+        <v>第 1 周：老师看向你时保持目光接触</v>
+      </c>
+      <c r="D91" t="str">
+        <v>第 1 周：老师看向你时保持目光接触</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>SC_RX_22</v>
+      </c>
+      <c r="B92" t="str">
+        <v>3</v>
+      </c>
+      <c r="C92" t="str">
+        <v>第 2 周：知道答案时在心里说一遍</v>
+      </c>
+      <c r="D92" t="str">
+        <v>第 2 周：知道答案时在心里说一遍</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>SC_RX_22</v>
+      </c>
+      <c r="B93" t="str">
+        <v>4</v>
+      </c>
+      <c r="C93" t="str">
+        <v>第 3 周：对同桌小声说出答案</v>
+      </c>
+      <c r="D93" t="str">
+        <v>第 3 周：对同桌小声说出答案</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>SC_RX_22</v>
+      </c>
+      <c r="B94" t="str">
+        <v>5</v>
+      </c>
+      <c r="C94" t="str">
+        <v>第 4 周：举手一次（事先与老师约定，老师会叫你</v>
+      </c>
+      <c r="D94" t="str">
+        <v>第 4 周：举手一次（事先与老师约定，老师会叫你），每完成一阶段给具体口头表扬</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>SC_RX_23</v>
+      </c>
+      <c r="B95" t="str">
+        <v>1</v>
+      </c>
+      <c r="C95" t="str">
+        <v>第一步·共定目标：具体可测（不是「认真听讲」而是</v>
+      </c>
+      <c r="D95" t="str">
+        <v>第一步·共定目标：具体可测（不是「认真听讲」而是「老师叫我名字时我能站起来」）</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>SC_RX_23</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2</v>
+      </c>
+      <c r="C96" t="str">
+        <v>第二步·明确奖励：首选社会性奖励（额外自由时间/</v>
+      </c>
+      <c r="D96" t="str">
+        <v>第二步·明确奖励：首选社会性奖励（额外自由时间/当小助手/优先选择权），物质奖励辅助</v>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>SC_RX_23</v>
+      </c>
+      <c r="B97" t="str">
+        <v>3</v>
+      </c>
+      <c r="C97" t="str">
+        <v>第三步·每日复盘：放学最后 2 分钟 30 秒复</v>
+      </c>
+      <c r="D97" t="str">
+        <v>第三步·每日复盘：放学最后 2 分钟 30 秒复盘——做到了吗？为什么？明天怎么调整？</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>SC_RX_23</v>
+      </c>
+      <c r="B98" t="str">
+        <v>4</v>
+      </c>
+      <c r="C98" t="str">
+        <v>依恋增强版：增加关系目标——「这一周当你沮丧或想</v>
+      </c>
+      <c r="D98" t="str">
+        <v>依恋增强版：增加关系目标——「这一周当你沮丧或想发火时，可以来找我，我们一起想办法」</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>SC_RX_24</v>
+      </c>
+      <c r="B99" t="str">
+        <v>1</v>
+      </c>
+      <c r="C99" t="str">
+        <v>在 S4 方案中增设 S4-relation 目</v>
+      </c>
+      <c r="D99" t="str">
+        <v>在 S4 方案中增设 S4-relation 目标（不单独作为结案标准，与行为目标并列记录）</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>SC_RX_24</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2</v>
+      </c>
+      <c r="C100" t="str">
+        <v>关系修复≠「让学生喜欢我」＝「让学生感受到这个关</v>
+      </c>
+      <c r="D100" t="str">
+        <v>关系修复≠「让学生喜欢我」＝「让学生感受到这个关系是安全的、可预测的」</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>SC_RX_24</v>
+      </c>
+      <c r="B101" t="str">
+        <v>3</v>
+      </c>
+      <c r="C101" t="str">
+        <v>以周为周期评估：学生主动发起互动的次数是否上升</v>
+      </c>
+      <c r="D101" t="str">
+        <v>以周为周期评估：学生主动发起互动的次数是否上升</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>SC_RX_24</v>
+      </c>
+      <c r="B102" t="str">
+        <v>4</v>
+      </c>
+      <c r="C102" t="str">
+        <v>行为目标反复失败→先检查关系目标进展（不是技术问</v>
+      </c>
+      <c r="D102" t="str">
+        <v>行为目标反复失败→先检查关系目标进展（不是技术问题而是关系问题）</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>SC_RX_25</v>
+      </c>
+      <c r="B103" t="str">
+        <v>1</v>
+      </c>
+      <c r="C103" t="str">
+        <v>S1 命名情绪（不先解决问题）：低年级——「我看</v>
+      </c>
+      <c r="D103" t="str">
+        <v>S1 命名情绪（不先解决问题）：低年级——「我看到你拳头攥得很紧，是叫「生气」吗？」；高年级——「用一个词形容你现在的心情」</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>SC_RX_25</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2</v>
+      </c>
+      <c r="C104" t="str">
+        <v>S2 接纳情绪：「谢谢你告诉我。生气或难过是正常</v>
+      </c>
+      <c r="D104" t="str">
+        <v>S2 接纳情绪：「谢谢你告诉我。生气或难过是正常的，每个人都会有。」</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>SC_RX_25</v>
+      </c>
+      <c r="B105" t="str">
+        <v>3</v>
+      </c>
+      <c r="C105" t="str">
+        <v>S3 才进入问题解决</v>
+      </c>
+      <c r="D105" t="str">
+        <v>S3 才进入问题解决</v>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>SC_RX_25</v>
+      </c>
+      <c r="B106" t="str">
+        <v>4</v>
+      </c>
+      <c r="C106" t="str">
+        <v>依恋增强版：增加无条件接纳表述——「无论你是因为</v>
+      </c>
+      <c r="D106" t="str">
+        <v>依恋增强版：增加无条件接纳表述——「无论你是因为什么有这种感觉，你都可以告诉我。我在这里陪着你」</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>SC_RX_26</v>
+      </c>
+      <c r="B107" t="str">
+        <v>1</v>
+      </c>
+      <c r="C107" t="str">
+        <v>启动前调取该生优势测评 Top2-3 类型，优点</v>
+      </c>
+      <c r="D107" t="str">
+        <v>启动前调取该生优势测评 Top2-3 类型，优点选择优先从优势领域切入</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>SC_RX_26</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Step 0（依恋增强版·关系预热）：「我想和你</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Step 0（依恋增强版·关系预热）：「我想和你一起发现你的优点——不是因为你做错了什么，而是因为我想更多地了解你好的那一面」</v>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>SC_RX_26</v>
+      </c>
+      <c r="B109" t="str">
+        <v>3</v>
+      </c>
+      <c r="C109" t="str">
+        <v>S1 每天找 1-2 件「今天我做得不错的事」，</v>
+      </c>
+      <c r="D109" t="str">
+        <v>S1 每天找 1-2 件「今天我做得不错的事」，具体到行为</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>SC_RX_26</v>
+      </c>
+      <c r="B110" t="str">
+        <v>4</v>
+      </c>
+      <c r="C110" t="str">
+        <v>S2 累计一周后在班会上以「本周 XX 之星」等</v>
+      </c>
+      <c r="D110" t="str">
+        <v>S2 累计一周后在班会上以「本周 XX 之星」等形式公开肯定</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>SC_RX_26</v>
+      </c>
+      <c r="B111" t="str">
+        <v>5</v>
+      </c>
+      <c r="C111" t="str">
+        <v>S3 连续 4 周后让孩子自己写，老师逐步退出</v>
+      </c>
+      <c r="D111" t="str">
+        <v>S3 连续 4 周后让孩子自己写，老师逐步退出</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>SC_RX_27</v>
+      </c>
+      <c r="B112" t="str">
+        <v>1</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Step 0（依恋增强版·安全基地预热）：1-2</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Step 0（依恋增强版·安全基地预热）：1-2 分钟轻松对话，让学生感受「此刻我是安全的，这个人不会评判我」</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>SC_RX_27</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2</v>
+      </c>
+      <c r="C113" t="str">
+        <v>S1 设计简短社交剧本——「走近正在玩的小组，站</v>
+      </c>
+      <c r="D113" t="str">
+        <v>S1 设计简短社交剧本——「走近正在玩的小组，站旁边看 30 秒，等一个自然停顿，说「看起来好好玩，我可以加入吗？」」</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>SC_RX_27</v>
+      </c>
+      <c r="B114" t="str">
+        <v>3</v>
+      </c>
+      <c r="C114" t="str">
+        <v>S2 老师先做示范表演，再让孩子练习 3 遍</v>
+      </c>
+      <c r="D114" t="str">
+        <v>S2 老师先做示范表演，再让孩子练习 3 遍</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>SC_RX_27</v>
+      </c>
+      <c r="B115" t="str">
+        <v>4</v>
+      </c>
+      <c r="C115" t="str">
+        <v>S3 在真实场景中观察使用情况，当天给反馈</v>
+      </c>
+      <c r="D115" t="str">
+        <v>S3 在真实场景中观察使用情况，当天给反馈</v>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>SC_RX_28</v>
+      </c>
+      <c r="B116" t="str">
+        <v>1</v>
+      </c>
+      <c r="C116" t="str">
+        <v>S1 安排性格温和、社交能力中等的同伴坐在旁边（</v>
+      </c>
+      <c r="D116" t="str">
+        <v>S1 安排性格温和、社交能力中等的同伴坐在旁边（不选最强的——碾压式配对适得其反）</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>SC_RX_28</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2</v>
+      </c>
+      <c r="C117" t="str">
+        <v>S2 设计需要两人协作才能完成的任务</v>
+      </c>
+      <c r="D117" t="str">
+        <v>S2 设计需要两人协作才能完成的任务</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>SC_RX_28</v>
+      </c>
+      <c r="B118" t="str">
+        <v>3</v>
+      </c>
+      <c r="C118" t="str">
+        <v>S3 从「任务导向的互动」自然过渡到「社交导向的</v>
+      </c>
+      <c r="D118" t="str">
+        <v>S3 从「任务导向的互动」自然过渡到「社交导向的互动」</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>SC_RX_28</v>
+      </c>
+      <c r="B119" t="str">
+        <v>4</v>
+      </c>
+      <c r="C119" t="str">
+        <v>S4 每周末分别问双方感受</v>
+      </c>
+      <c r="D119" t="str">
+        <v>S4 每周末分别问双方感受</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>SC_RX_28</v>
+      </c>
+      <c r="B120" t="str">
+        <v>5</v>
+      </c>
+      <c r="C120" t="str">
+        <v>依恋增强版：配对前单独沟通同伴——「XX 同学需</v>
+      </c>
+      <c r="D120" t="str">
+        <v>依恋增强版：配对前单独沟通同伴——「XX 同学需要一个朋友，我想请你帮忙……这不是任务，是邀请」</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>SC_RX_29</v>
+      </c>
+      <c r="B121" t="str">
+        <v>1</v>
+      </c>
+      <c r="C121" t="str">
+        <v>S1 优势定位：从优势测评获取 Top2-3 优</v>
+      </c>
+      <c r="D121" t="str">
+        <v>S1 优势定位：从优势测评获取 Top2-3 优势类型（1-2 年级 50 题版/3-6 年级 20 题版），未测评→安排测评或教师观察法</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>SC_RX_29</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2</v>
+      </c>
+      <c r="C122" t="str">
+        <v>S2 优势-问题匹配：优势类型与问题编码交叉分析</v>
+      </c>
+      <c r="D122" t="str">
+        <v>S2 优势-问题匹配：优势类型与问题编码交叉分析，「用优势通道解决弱势问题」</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>SC_RX_29</v>
+      </c>
+      <c r="B123" t="str">
+        <v>3</v>
+      </c>
+      <c r="C123" t="str">
+        <v>S3 优势嵌入式方案：格式「主技术 T1+优势适</v>
+      </c>
+      <c r="D123" t="str">
+        <v>S3 优势嵌入式方案：格式「主技术 T1+优势适配：因该生身体动觉型，将休息奖励改为 1 分钟运动」</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>SC_RX_29</v>
+      </c>
+      <c r="B124" t="str">
+        <v>4</v>
+      </c>
+      <c r="C124" t="str">
+        <v>S4 验证优势假设：执行 2 周后评估，无效→检</v>
+      </c>
+      <c r="D124" t="str">
+        <v>S4 验证优势假设：执行 2 周后评估，无效→检查优势定位准确性与匹配合理性，必要时回到 S1</v>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>SC_RX_30</v>
+      </c>
+      <c r="B125" t="str">
+        <v>1</v>
+      </c>
+      <c r="C125" t="str">
+        <v>在优势定位后增加优势验证——不告诉学生「你有这个</v>
+      </c>
+      <c r="D125" t="str">
+        <v>在优势定位后增加优势验证——不告诉学生「你有这个优势」，而是通过具体活动让他「体验」到</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>SC_RX_30</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2</v>
+      </c>
+      <c r="C126" t="str">
+        <v>例：空间智能→拼装任务让他「做出来」；人类型→帮</v>
+      </c>
+      <c r="D126" t="str">
+        <v>例：空间智能→拼装任务让他「做出来」；人类型→帮助小同学完成一件事</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>SC_RX_30</v>
+      </c>
+      <c r="B127" t="str">
+        <v>3</v>
+      </c>
+      <c r="C127" t="str">
+        <v>任务完成后不急着表扬，问：「你觉得你刚才做了什么</v>
+      </c>
+      <c r="D127" t="str">
+        <v>任务完成后不急着表扬，问：「你觉得你刚才做了什么让你自己觉得挺厉害？」</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>SC_RX_30</v>
+      </c>
+      <c r="B128" t="str">
+        <v>4</v>
+      </c>
+      <c r="C128" t="str">
+        <v>引导他自己命名优势体验</v>
+      </c>
+      <c r="D128" t="str">
+        <v>引导他自己命名优势体验</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="B129" t="str">
+        <v>1</v>
+      </c>
+      <c r="C129" t="str">
+        <v>S1 看见情绪（识别）：「我看到你攥紧拳头/眼睛</v>
+      </c>
+      <c r="D129" t="str">
+        <v>S1 看见情绪（识别）：「我看到你攥紧拳头/眼睛红了/声音在发抖……」</v>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="B130" t="str">
+        <v>2</v>
+      </c>
+      <c r="C130" t="str">
+        <v>S2 命名情绪（表达）：「你现在的感觉，是不是叫</v>
+      </c>
+      <c r="D130" t="str">
+        <v>S2 命名情绪（表达）：「你现在的感觉，是不是叫「生气」/「委屈」/「害怕」？」（低年级可用 6 张基础情绪卡片）</v>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="B131" t="str">
+        <v>3</v>
+      </c>
+      <c r="C131" t="str">
+        <v>S3 接纳情绪（调控）：「有这样的感觉是正常的。</v>
+      </c>
+      <c r="D131" t="str">
+        <v>S3 接纳情绪（调控）：「有这样的感觉是正常的。谢谢你告诉我。」（接纳的是情绪，规范的是行为）</v>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="B132" t="str">
+        <v>4</v>
+      </c>
+      <c r="C132" t="str">
+        <v>S4 连接需求（心智化升级）：「你觉得刚才那么生</v>
+      </c>
+      <c r="D132" t="str">
+        <v>S4 连接需求（心智化升级）：「你觉得刚才那么生气，是因为想要什么？」</v>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>SC_RX_31</v>
+      </c>
+      <c r="B133" t="str">
+        <v>5</v>
+      </c>
+      <c r="C133" t="str">
+        <v>班级层面：每天 1 次情绪天气（30 秒）；冲突</v>
+      </c>
+      <c r="D133" t="str">
+        <v>班级层面：每天 1 次情绪天气（30 秒）；冲突调解三步心智化；教师自我心智化复盘</v>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J133"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2016,32 +8222,9 @@
         <v>依据</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SC_RX_06</v>
-      </c>
-      <c r="B2" t="str">
-        <v>学生已在专业干预中</v>
-      </c>
-      <c r="C2" t="str">
-        <v>warn</v>
-      </c>
-      <c r="D2" t="str">
-        <v>避免重复动员造成学生压力</v>
-      </c>
-      <c r="E2" t="str">
-        <v>与心理专员确认现有干预方案后再行动</v>
-      </c>
-      <c r="F2" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="G2" t="str">
-        <v>学生个体问题手册v1</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>